--- a/public/exports/29189579.xlsx
+++ b/public/exports/29189579.xlsx
@@ -331,16 +331,16 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">381215, 381216</t>
+          <t xml:space="preserve">380712</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F7">
-        <v>3975</v>
+        <v>414</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -381,16 +381,16 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">382049, 382050</t>
+          <t xml:space="preserve">381206, 381207</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F8">
-        <v>579</v>
+        <v>1717</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -431,16 +431,16 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">382050</t>
+          <t xml:space="preserve">381215, 381216</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F9">
-        <v>403</v>
+        <v>3975</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -481,16 +481,16 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">4050055</t>
+          <t xml:space="preserve">381665, 381666</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F10">
-        <v>337</v>
+        <v>844</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -531,7 +531,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4050055</t>
+          <t xml:space="preserve">382049, 382050</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -540,7 +540,7 @@
         </is>
       </c>
       <c r="F11">
-        <v>740</v>
+        <v>579</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -581,16 +581,16 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">4050055</t>
+          <t xml:space="preserve">382050</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F12">
-        <v>1219</v>
+        <v>403</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -631,16 +631,16 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">4057006</t>
+          <t xml:space="preserve">382557, 382558, 382559</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F13">
-        <v>481</v>
+        <v>1019</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -681,16 +681,16 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">4057006</t>
+          <t xml:space="preserve">4050055</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F14">
-        <v>472</v>
+        <v>337</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -731,16 +731,16 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">4058695</t>
+          <t xml:space="preserve">4050055</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F15">
-        <v>2067</v>
+        <v>740</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -781,16 +781,16 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">4059356</t>
+          <t xml:space="preserve">4050055</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">44</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F16">
-        <v>256</v>
+        <v>1219</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -831,7 +831,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">4060423</t>
+          <t xml:space="preserve">4058695</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -840,7 +840,7 @@
         </is>
       </c>
       <c r="F17">
-        <v>6657</v>
+        <v>2067</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -881,16 +881,16 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">4062711</t>
+          <t xml:space="preserve">4059356</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">44</t>
         </is>
       </c>
       <c r="F18">
-        <v>1113</v>
+        <v>256</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -931,16 +931,16 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">4062711</t>
+          <t xml:space="preserve">4060423</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F19">
-        <v>926</v>
+        <v>6657</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -981,16 +981,16 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">4066849</t>
+          <t xml:space="preserve">4062711</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F20">
-        <v>665</v>
+        <v>1113</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1031,16 +1031,16 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">4070705</t>
+          <t xml:space="preserve">4062711</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F21">
-        <v>2564</v>
+        <v>926</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1081,16 +1081,16 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">4074902</t>
+          <t xml:space="preserve">4066849</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F22">
-        <v>743</v>
+        <v>665</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1131,16 +1131,16 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">4508315</t>
+          <t xml:space="preserve">4070705</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F23">
-        <v>1525</v>
+        <v>2564</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1181,16 +1181,16 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">500024, 500025, 100014875, 500026</t>
+          <t xml:space="preserve">4074902</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F24">
-        <v>2946</v>
+        <v>743</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1231,7 +1231,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">5575087</t>
+          <t xml:space="preserve">500024, 500025, 100014875, 500026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="F25">
-        <v>1072</v>
+        <v>2946</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1281,16 +1281,16 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">5575173</t>
+          <t xml:space="preserve">5575087</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F26">
-        <v>3510</v>
+        <v>1072</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1331,16 +1331,16 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">5575834</t>
+          <t xml:space="preserve">5575173</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F27">
-        <v>513</v>
+        <v>3510</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1381,16 +1381,16 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">5575936</t>
+          <t xml:space="preserve">5575834</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F28">
-        <v>428</v>
+        <v>513</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1436,11 +1436,11 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F29">
-        <v>1377</v>
+        <v>428</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1486,11 +1486,11 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F30">
-        <v>418</v>
+        <v>1377</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1531,16 +1531,16 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">5578173</t>
+          <t xml:space="preserve">5575936</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F31">
-        <v>813</v>
+        <v>418</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1586,11 +1586,11 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F32">
-        <v>531</v>
+        <v>813</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1631,16 +1631,16 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">5578628</t>
+          <t xml:space="preserve">5578173</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F33">
-        <v>466</v>
+        <v>531</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1681,16 +1681,16 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">5579321</t>
+          <t xml:space="preserve">5578628</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F34">
-        <v>509</v>
+        <v>466</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1731,16 +1731,16 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">5579425</t>
+          <t xml:space="preserve">5579321</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F35">
-        <v>283</v>
+        <v>509</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1781,7 +1781,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">5579990</t>
+          <t xml:space="preserve">5579425</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1790,7 +1790,7 @@
         </is>
       </c>
       <c r="F36">
-        <v>9077</v>
+        <v>283</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1831,16 +1831,16 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">5580769</t>
+          <t xml:space="preserve">5579990</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F37">
-        <v>388</v>
+        <v>9077</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -1881,16 +1881,16 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">5581093</t>
+          <t xml:space="preserve">5580769</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F38">
-        <v>496</v>
+        <v>388</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -1931,16 +1931,16 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">5581102</t>
+          <t xml:space="preserve">5581093</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F39">
-        <v>1040</v>
+        <v>496</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -1981,16 +1981,16 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">5581674</t>
+          <t xml:space="preserve">5581102</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F40">
-        <v>284</v>
+        <v>1040</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -2031,16 +2031,16 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">5581674</t>
+          <t xml:space="preserve">5582112</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="F41">
-        <v>536</v>
+        <v>1112</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -2081,16 +2081,16 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">5581674</t>
+          <t xml:space="preserve">5582112</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="F42">
-        <v>616</v>
+        <v>748</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -2131,16 +2131,16 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">5581674</t>
+          <t xml:space="preserve">5582112</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="F43">
-        <v>260</v>
+        <v>1496</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -2186,11 +2186,11 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="F44">
-        <v>1112</v>
+        <v>584</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -2236,11 +2236,11 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="F45">
-        <v>748</v>
+        <v>593</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -2286,11 +2286,11 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="F46">
-        <v>1496</v>
+        <v>304</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -2336,11 +2336,11 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">24</t>
         </is>
       </c>
       <c r="F47">
-        <v>584</v>
+        <v>1507</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -2386,11 +2386,11 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F48">
-        <v>593</v>
+        <v>912</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -2436,11 +2436,11 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F49">
-        <v>304</v>
+        <v>1268</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2486,11 +2486,11 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t xml:space="preserve">24</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F50">
-        <v>1507</v>
+        <v>285</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2536,11 +2536,11 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F51">
-        <v>912</v>
+        <v>340</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2586,11 +2586,11 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F52">
-        <v>1268</v>
+        <v>336</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -2636,11 +2636,11 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F53">
-        <v>285</v>
+        <v>754</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -2681,16 +2681,16 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t xml:space="preserve">5582112</t>
+          <t xml:space="preserve">5582842</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F54">
-        <v>340</v>
+        <v>984</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -2731,16 +2731,16 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t xml:space="preserve">5582112</t>
+          <t xml:space="preserve">5584332</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F55">
-        <v>336</v>
+        <v>9131</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -2781,16 +2781,16 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t xml:space="preserve">5582112</t>
+          <t xml:space="preserve">7046491</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F56">
-        <v>754</v>
+        <v>809</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -2831,7 +2831,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t xml:space="preserve">5582842</t>
+          <t xml:space="preserve">748075, 5579184</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -2840,7 +2840,7 @@
         </is>
       </c>
       <c r="F57">
-        <v>984</v>
+        <v>1673</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -2881,16 +2881,16 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t xml:space="preserve">5584332</t>
+          <t xml:space="preserve">748077, 5579353</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F58">
-        <v>9131</v>
+        <v>748</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -2931,7 +2931,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t xml:space="preserve">7046491</t>
+          <t xml:space="preserve">748079, 5579359</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -2940,7 +2940,7 @@
         </is>
       </c>
       <c r="F59">
-        <v>809</v>
+        <v>680</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -2981,16 +2981,16 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t xml:space="preserve">748075, 5579184</t>
+          <t xml:space="preserve">748079, 5579359</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F60">
-        <v>1673</v>
+        <v>700</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -3031,16 +3031,16 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t xml:space="preserve">748077, 5579353</t>
+          <t xml:space="preserve">748079, 5579359</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F61">
-        <v>748</v>
+        <v>866</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -3081,7 +3081,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t xml:space="preserve">748079, 5579359</t>
+          <t xml:space="preserve">748081, 5579361</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -3090,7 +3090,7 @@
         </is>
       </c>
       <c r="F62">
-        <v>680</v>
+        <v>1152</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -3131,16 +3131,16 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t xml:space="preserve">748079, 5579359</t>
+          <t xml:space="preserve">748082, 5579362</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F63">
-        <v>700</v>
+        <v>2229</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -3181,16 +3181,16 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t xml:space="preserve">748079, 5579359</t>
+          <t xml:space="preserve">748085, 5579377</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F64">
-        <v>866</v>
+        <v>1732</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -3231,7 +3231,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t xml:space="preserve">748081, 5579361</t>
+          <t xml:space="preserve">748090, 5579318</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -3240,7 +3240,7 @@
         </is>
       </c>
       <c r="F65">
-        <v>1152</v>
+        <v>574</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -3281,16 +3281,16 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t xml:space="preserve">748082, 5579362</t>
+          <t xml:space="preserve">748091, 100013151</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F66">
-        <v>2229</v>
+        <v>889</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -3331,7 +3331,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t xml:space="preserve">748085, 5579377</t>
+          <t xml:space="preserve">748145, 4066935</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -3340,7 +3340,7 @@
         </is>
       </c>
       <c r="F67">
-        <v>1732</v>
+        <v>287</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -3381,7 +3381,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t xml:space="preserve">748090, 5579318</t>
+          <t xml:space="preserve">748266, 100075804</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -3390,7 +3390,7 @@
         </is>
       </c>
       <c r="F68">
-        <v>574</v>
+        <v>682</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -3431,7 +3431,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t xml:space="preserve">748091, 100013151</t>
+          <t xml:space="preserve">748295, 7382442</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -3440,7 +3440,7 @@
         </is>
       </c>
       <c r="F69">
-        <v>889</v>
+        <v>447</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -3481,16 +3481,16 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t xml:space="preserve">748145, 4066935</t>
+          <t xml:space="preserve">748320, 9376480</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F70">
-        <v>287</v>
+        <v>280</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -3531,16 +3531,16 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t xml:space="preserve">748266, 100075804</t>
+          <t xml:space="preserve">748322, 9012346</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F71">
-        <v>682</v>
+        <v>525</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
@@ -3581,16 +3581,16 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t xml:space="preserve">748295, 7382442</t>
+          <t xml:space="preserve">748323, 4049713</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F72">
-        <v>447</v>
+        <v>306</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -3631,16 +3631,16 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t xml:space="preserve">748320, 9376480</t>
+          <t xml:space="preserve">748327, 4049692</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F73">
-        <v>280</v>
+        <v>289</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -3681,16 +3681,16 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t xml:space="preserve">748322, 9012346</t>
+          <t xml:space="preserve">748332, 9524232</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F74">
-        <v>525</v>
+        <v>293</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -3731,16 +3731,16 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t xml:space="preserve">748323, 4049713</t>
+          <t xml:space="preserve">748334, 5580236</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F75">
-        <v>306</v>
+        <v>1267</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -3781,16 +3781,16 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t xml:space="preserve">748327, 4049692</t>
+          <t xml:space="preserve">748336, 8899388</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F76">
-        <v>289</v>
+        <v>490</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
@@ -3831,7 +3831,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t xml:space="preserve">748332, 9524232</t>
+          <t xml:space="preserve">748337, 4508603</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -3840,7 +3840,7 @@
         </is>
       </c>
       <c r="F77">
-        <v>293</v>
+        <v>277</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -3881,16 +3881,16 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t xml:space="preserve">748334, 5580236</t>
+          <t xml:space="preserve">748353, 8811417</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F78">
-        <v>1267</v>
+        <v>1233</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
@@ -3931,16 +3931,16 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t xml:space="preserve">748336, 8899388</t>
+          <t xml:space="preserve">748353, 8811417</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F79">
-        <v>490</v>
+        <v>10931</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
@@ -3981,16 +3981,16 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t xml:space="preserve">748337, 4508603</t>
+          <t xml:space="preserve">748359, 4070602</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F80">
-        <v>277</v>
+        <v>409</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
@@ -4031,7 +4031,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t xml:space="preserve">748353, 8811417</t>
+          <t xml:space="preserve">7870665</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -4040,7 +4040,7 @@
         </is>
       </c>
       <c r="F81">
-        <v>1233</v>
+        <v>2919</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
@@ -4081,16 +4081,16 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t xml:space="preserve">748353, 8811417</t>
+          <t xml:space="preserve">8116502</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="F82">
-        <v>10931</v>
+        <v>392</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
@@ -4131,16 +4131,16 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t xml:space="preserve">748359, 4070602</t>
+          <t xml:space="preserve">8116502</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="F83">
-        <v>409</v>
+        <v>496</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t xml:space="preserve">7870665</t>
+          <t xml:space="preserve">8184585</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -4190,7 +4190,7 @@
         </is>
       </c>
       <c r="F84">
-        <v>2919</v>
+        <v>1006</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
@@ -4231,16 +4231,16 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t xml:space="preserve">8116502</t>
+          <t xml:space="preserve">8268606</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F85">
-        <v>392</v>
+        <v>417</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
@@ -4281,16 +4281,16 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t xml:space="preserve">8116502</t>
+          <t xml:space="preserve">8268606</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F86">
-        <v>496</v>
+        <v>300</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
@@ -4331,7 +4331,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t xml:space="preserve">8184585</t>
+          <t xml:space="preserve">8395726</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -4340,7 +4340,7 @@
         </is>
       </c>
       <c r="F87">
-        <v>1006</v>
+        <v>404</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
@@ -4381,7 +4381,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t xml:space="preserve">8268606</t>
+          <t xml:space="preserve">8798252</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -4390,7 +4390,7 @@
         </is>
       </c>
       <c r="F88">
-        <v>417</v>
+        <v>2716</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
@@ -4431,16 +4431,16 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t xml:space="preserve">8268606</t>
+          <t xml:space="preserve">8882814, 100623370</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F89">
-        <v>300</v>
+        <v>445</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
@@ -4481,7 +4481,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t xml:space="preserve">8395726</t>
+          <t xml:space="preserve">9391734</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -4490,7 +4490,7 @@
         </is>
       </c>
       <c r="F90">
-        <v>404</v>
+        <v>1776</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
@@ -4531,7 +4531,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t xml:space="preserve">8798252</t>
+          <t xml:space="preserve">9681144</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -4540,7 +4540,7 @@
         </is>
       </c>
       <c r="F91">
-        <v>2716</v>
+        <v>3176</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
@@ -4581,16 +4581,16 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t xml:space="preserve">8882814, 100623370</t>
+          <t xml:space="preserve">9875681</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F92">
-        <v>445</v>
+        <v>1806</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
@@ -4631,16 +4631,16 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t xml:space="preserve">8899482</t>
+          <t xml:space="preserve">9961833</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F93">
-        <v>252</v>
+        <v>593</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
@@ -4681,30 +4681,30 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t xml:space="preserve">8899482</t>
+          <t xml:space="preserve">4062734</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F94">
-        <v>1260</v>
+        <v>591</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200015802</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-06-24</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t xml:space="preserve">9391734</t>
+          <t xml:space="preserve">9815958</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -4740,21 +4740,21 @@
         </is>
       </c>
       <c r="F95">
-        <v>1776</v>
+        <v>766</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200027486</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2020-02-01</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -4781,30 +4781,30 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t xml:space="preserve">9681144</t>
+          <t xml:space="preserve">9815958</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F96">
-        <v>3176</v>
+        <v>436</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200027494</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2020-02-01</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -4844,17 +4844,17 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200027494</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2020-02-01</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -4894,17 +4894,17 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200027494</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2020-02-01</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -4931,30 +4931,30 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t xml:space="preserve">9875681</t>
+          <t xml:space="preserve">9815958</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F99">
-        <v>1806</v>
+        <v>296</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200027548</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2020-02-02</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -4981,30 +4981,30 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t xml:space="preserve">9961833</t>
+          <t xml:space="preserve">4075942</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F100">
-        <v>593</v>
+        <v>1315</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200029108</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2020-03-12</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -5031,25 +5031,25 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t xml:space="preserve">4062734</t>
+          <t xml:space="preserve">4508315</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="F101">
-        <v>591</v>
+        <v>1525</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t xml:space="preserve">200015802</t>
+          <t xml:space="preserve">200040147</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-06-24</t>
+          <t xml:space="preserve">2020-11-01</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -5081,25 +5081,25 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t xml:space="preserve">9815958</t>
+          <t xml:space="preserve">4057006</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F102">
-        <v>766</v>
+        <v>481</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t xml:space="preserve">200027486</t>
+          <t xml:space="preserve">200044236</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-02-01</t>
+          <t xml:space="preserve">2021-01-12</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -5131,25 +5131,25 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t xml:space="preserve">9815958</t>
+          <t xml:space="preserve">4057006</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F103">
-        <v>436</v>
+        <v>472</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t xml:space="preserve">200027518</t>
+          <t xml:space="preserve">200044236</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-02-01</t>
+          <t xml:space="preserve">2021-01-12</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -5181,25 +5181,25 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t xml:space="preserve">9815958</t>
+          <t xml:space="preserve">8184584</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F104">
-        <v>296</v>
+        <v>475</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t xml:space="preserve">200027548</t>
+          <t xml:space="preserve">200045482</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-02-02</t>
+          <t xml:space="preserve">2021-02-10</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -5231,25 +5231,25 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t xml:space="preserve">4075942</t>
+          <t xml:space="preserve">8184584</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F105">
-        <v>1315</v>
+        <v>452</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t xml:space="preserve">200029108</t>
+          <t xml:space="preserve">200045483</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-03-12</t>
+          <t xml:space="preserve">2021-02-10</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -5281,25 +5281,25 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t xml:space="preserve">8899482</t>
+          <t xml:space="preserve">8184584</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F106">
-        <v>434</v>
+        <v>532</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t xml:space="preserve">200039780</t>
+          <t xml:space="preserve">200045484</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-10-26</t>
+          <t xml:space="preserve">2021-02-10</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -5336,15 +5336,15 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F107">
-        <v>475</v>
+        <v>445</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t xml:space="preserve">200045482</t>
+          <t xml:space="preserve">200045485</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -5381,25 +5381,25 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t xml:space="preserve">8184584</t>
+          <t xml:space="preserve">8798318</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F108">
-        <v>452</v>
+        <v>403</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t xml:space="preserve">200045483</t>
+          <t xml:space="preserve">310017203</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-02-10</t>
+          <t xml:space="preserve">2022-12-12</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -5431,25 +5431,25 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t xml:space="preserve">8184584</t>
+          <t xml:space="preserve">5580269</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F109">
-        <v>532</v>
+        <v>272</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t xml:space="preserve">200045484</t>
+          <t xml:space="preserve">311071797</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-02-10</t>
+          <t xml:space="preserve">2024-09-04</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -5481,25 +5481,25 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t xml:space="preserve">8184584</t>
+          <t xml:space="preserve">4074902</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F110">
-        <v>445</v>
+        <v>872</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t xml:space="preserve">200045485</t>
+          <t xml:space="preserve">311156172</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-02-10</t>
+          <t xml:space="preserve">2026-01-29</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -5531,7 +5531,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t xml:space="preserve">8798318</t>
+          <t xml:space="preserve">8724731</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -5540,16 +5540,16 @@
         </is>
       </c>
       <c r="F111">
-        <v>403</v>
+        <v>358</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t xml:space="preserve">310017203</t>
+          <t xml:space="preserve">311197742</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t xml:space="preserve">2022-12-12</t>
+          <t xml:space="preserve">2026-08-31</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -5581,35 +5581,35 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t xml:space="preserve">5580269</t>
+          <t xml:space="preserve">4050024</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F112">
-        <v>272</v>
+        <v>531</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t xml:space="preserve">311071797</t>
+          <t xml:space="preserve">311198907</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t xml:space="preserve">2024-09-04</t>
+          <t xml:space="preserve">2026-09-06</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -5631,7 +5631,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t xml:space="preserve">382557, 382558, 382559</t>
+          <t xml:space="preserve">4050055</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -5640,26 +5640,26 @@
         </is>
       </c>
       <c r="F113">
-        <v>1019</v>
+        <v>6478</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t xml:space="preserve">311074127</t>
+          <t xml:space="preserve">311199661</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t xml:space="preserve">2024-09-18</t>
+          <t xml:space="preserve">2026-09-09</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -5681,35 +5681,35 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t xml:space="preserve">4074902</t>
+          <t xml:space="preserve">4055746</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F114">
-        <v>872</v>
+        <v>259</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t xml:space="preserve">311156172</t>
+          <t xml:space="preserve">311199649</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-29</t>
+          <t xml:space="preserve">2026-09-09</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -5731,35 +5731,35 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t xml:space="preserve">8724731</t>
+          <t xml:space="preserve">8899384</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F115">
-        <v>358</v>
+        <v>882</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t xml:space="preserve">311197742</t>
+          <t xml:space="preserve">311199648</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-31</t>
+          <t xml:space="preserve">2026-09-09</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -5781,25 +5781,25 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t xml:space="preserve">4050024</t>
+          <t xml:space="preserve">4059105</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F116">
-        <v>531</v>
+        <v>292</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t xml:space="preserve">311198907</t>
+          <t xml:space="preserve">311201294</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-06</t>
+          <t xml:space="preserve">2026-09-19</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -5831,7 +5831,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t xml:space="preserve">4050055</t>
+          <t xml:space="preserve">7806050</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -5840,16 +5840,16 @@
         </is>
       </c>
       <c r="F117">
-        <v>6478</v>
+        <v>309</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t xml:space="preserve">311199661</t>
+          <t xml:space="preserve">311201293</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-09</t>
+          <t xml:space="preserve">2026-09-19</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -5881,25 +5881,25 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t xml:space="preserve">4055746</t>
+          <t xml:space="preserve">5577994</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F118">
-        <v>259</v>
+        <v>1009</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t xml:space="preserve">311199649</t>
+          <t xml:space="preserve">311204539</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-09</t>
+          <t xml:space="preserve">2026-10-05</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -5931,25 +5931,25 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t xml:space="preserve">8899384</t>
+          <t xml:space="preserve">5581102</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F119">
-        <v>882</v>
+        <v>9399</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t xml:space="preserve">311199648</t>
+          <t xml:space="preserve">311207277</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-09</t>
+          <t xml:space="preserve">2026-10-18</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -5981,25 +5981,25 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t xml:space="preserve">4059105</t>
+          <t xml:space="preserve">5575936</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F120">
-        <v>292</v>
+        <v>1791</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t xml:space="preserve">311201294</t>
+          <t xml:space="preserve">311213851</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-19</t>
+          <t xml:space="preserve">2026-11-23</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -6031,7 +6031,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t xml:space="preserve">7806050</t>
+          <t xml:space="preserve">4050673</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -6040,16 +6040,16 @@
         </is>
       </c>
       <c r="F121">
-        <v>309</v>
+        <v>580</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t xml:space="preserve">311201293</t>
+          <t xml:space="preserve">311215058</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-19</t>
+          <t xml:space="preserve">2026-11-30</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -6081,7 +6081,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t xml:space="preserve">8747981</t>
+          <t xml:space="preserve">4055731</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -6090,16 +6090,16 @@
         </is>
       </c>
       <c r="F122">
-        <v>369</v>
+        <v>1902</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t xml:space="preserve">311202010</t>
+          <t xml:space="preserve">311215076</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-22</t>
+          <t xml:space="preserve">2026-11-30</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t xml:space="preserve">5577994</t>
+          <t xml:space="preserve">5582112</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -6140,16 +6140,16 @@
         </is>
       </c>
       <c r="F123">
-        <v>1009</v>
+        <v>962</v>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t xml:space="preserve">311204539</t>
+          <t xml:space="preserve">311215617</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-05</t>
+          <t xml:space="preserve">2026-12-02</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -6181,25 +6181,25 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t xml:space="preserve">5581102</t>
+          <t xml:space="preserve">4068043</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F124">
-        <v>9399</v>
+        <v>1342</v>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t xml:space="preserve">311207277</t>
+          <t xml:space="preserve">311216682</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-18</t>
+          <t xml:space="preserve">2026-12-08</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -6231,25 +6231,25 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t xml:space="preserve">5575936</t>
+          <t xml:space="preserve">4068043</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F125">
-        <v>1791</v>
+        <v>2601</v>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t xml:space="preserve">311213851</t>
+          <t xml:space="preserve">311216682</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-23</t>
+          <t xml:space="preserve">2026-12-08</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -6281,25 +6281,25 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t xml:space="preserve">4050673</t>
+          <t xml:space="preserve">4068043</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F126">
-        <v>580</v>
+        <v>658</v>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t xml:space="preserve">311215058</t>
+          <t xml:space="preserve">311216682</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-30</t>
+          <t xml:space="preserve">2026-12-08</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -6331,25 +6331,25 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t xml:space="preserve">4055731</t>
+          <t xml:space="preserve">4068043</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F127">
-        <v>1902</v>
+        <v>269</v>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t xml:space="preserve">311215076</t>
+          <t xml:space="preserve">311216686</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-30</t>
+          <t xml:space="preserve">2026-12-08</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -6381,7 +6381,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t xml:space="preserve">5582112</t>
+          <t xml:space="preserve">4055746</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -6390,16 +6390,16 @@
         </is>
       </c>
       <c r="F128">
-        <v>962</v>
+        <v>1776</v>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t xml:space="preserve">311215617</t>
+          <t xml:space="preserve">311223000</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-02</t>
+          <t xml:space="preserve">2027-01-17</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -6431,25 +6431,25 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t xml:space="preserve">4068043</t>
+          <t xml:space="preserve">4057006</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F129">
-        <v>1342</v>
+        <v>1336</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t xml:space="preserve">311216682</t>
+          <t xml:space="preserve">311224661</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-08</t>
+          <t xml:space="preserve">2027-01-26</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -6481,25 +6481,25 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t xml:space="preserve">4068043</t>
+          <t xml:space="preserve">4057006</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F130">
-        <v>2601</v>
+        <v>1455</v>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t xml:space="preserve">311216682</t>
+          <t xml:space="preserve">311224665</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-08</t>
+          <t xml:space="preserve">2027-01-26</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -6531,25 +6531,25 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t xml:space="preserve">4068043</t>
+          <t xml:space="preserve">100007822</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F131">
-        <v>658</v>
+        <v>2115</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t xml:space="preserve">311216682</t>
+          <t xml:space="preserve">311248999</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-08</t>
+          <t xml:space="preserve">2027-05-22</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -6581,25 +6581,25 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t xml:space="preserve">4068043</t>
+          <t xml:space="preserve">4065067</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F132">
-        <v>269</v>
+        <v>1898</v>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t xml:space="preserve">311216686</t>
+          <t xml:space="preserve">311269956</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-08</t>
+          <t xml:space="preserve">2027-08-31</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -6631,25 +6631,25 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t xml:space="preserve">4055746</t>
+          <t xml:space="preserve">4065067</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F133">
-        <v>1776</v>
+        <v>1477</v>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t xml:space="preserve">311223000</t>
+          <t xml:space="preserve">311269956</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-01-17</t>
+          <t xml:space="preserve">2027-08-31</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -6681,7 +6681,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t xml:space="preserve">4057006</t>
+          <t xml:space="preserve">8116502</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -6690,16 +6690,16 @@
         </is>
       </c>
       <c r="F134">
-        <v>1336</v>
+        <v>1500</v>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t xml:space="preserve">311224661</t>
+          <t xml:space="preserve">311272174</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-01-26</t>
+          <t xml:space="preserve">2027-09-11</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -6731,25 +6731,25 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t xml:space="preserve">4057006</t>
+          <t xml:space="preserve">7893354</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F135">
-        <v>1455</v>
+        <v>1091</v>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t xml:space="preserve">311224665</t>
+          <t xml:space="preserve">311274198</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-01-26</t>
+          <t xml:space="preserve">2027-09-21</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -6781,7 +6781,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t xml:space="preserve">100007822</t>
+          <t xml:space="preserve">5581297</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -6790,16 +6790,16 @@
         </is>
       </c>
       <c r="F136">
-        <v>2115</v>
+        <v>947</v>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t xml:space="preserve">311248999</t>
+          <t xml:space="preserve">311274935</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-05-22</t>
+          <t xml:space="preserve">2027-09-25</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -6831,25 +6831,25 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t xml:space="preserve">380712</t>
+          <t xml:space="preserve">5582684</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F137">
-        <v>414</v>
+        <v>701</v>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t xml:space="preserve">311259954</t>
+          <t xml:space="preserve">311274934</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-10</t>
+          <t xml:space="preserve">2027-09-25</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -6881,7 +6881,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t xml:space="preserve">381206, 381207</t>
+          <t xml:space="preserve">9441948</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -6890,16 +6890,16 @@
         </is>
       </c>
       <c r="F138">
-        <v>1717</v>
+        <v>445</v>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t xml:space="preserve">311260356</t>
+          <t xml:space="preserve">311280025</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-12</t>
+          <t xml:space="preserve">2027-10-23</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -6931,25 +6931,25 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t xml:space="preserve">4065067</t>
+          <t xml:space="preserve">8899384</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F139">
-        <v>1898</v>
+        <v>1476</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t xml:space="preserve">311269956</t>
+          <t xml:space="preserve">311283220</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-08-31</t>
+          <t xml:space="preserve">2027-11-10</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -6981,25 +6981,25 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t xml:space="preserve">4065067</t>
+          <t xml:space="preserve">8899384</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="F140">
-        <v>1477</v>
+        <v>260</v>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t xml:space="preserve">311269956</t>
+          <t xml:space="preserve">311283218</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-08-31</t>
+          <t xml:space="preserve">2027-11-10</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -7031,25 +7031,25 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t xml:space="preserve">8116502</t>
+          <t xml:space="preserve">8899384</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F141">
-        <v>1500</v>
+        <v>5926</v>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t xml:space="preserve">311272174</t>
+          <t xml:space="preserve">311283462</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-09-11</t>
+          <t xml:space="preserve">2027-11-13</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -7081,7 +7081,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t xml:space="preserve">7893354</t>
+          <t xml:space="preserve">5575145</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -7090,16 +7090,16 @@
         </is>
       </c>
       <c r="F142">
-        <v>1091</v>
+        <v>337</v>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t xml:space="preserve">311274198</t>
+          <t xml:space="preserve">311284088</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-09-21</t>
+          <t xml:space="preserve">2027-11-16</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -7131,7 +7131,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t xml:space="preserve">5581297</t>
+          <t xml:space="preserve">5575376</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -7140,16 +7140,16 @@
         </is>
       </c>
       <c r="F143">
-        <v>947</v>
+        <v>590</v>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t xml:space="preserve">311274935</t>
+          <t xml:space="preserve">311285478</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-09-25</t>
+          <t xml:space="preserve">2027-11-23</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -7181,25 +7181,25 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t xml:space="preserve">5582684</t>
+          <t xml:space="preserve">4508315</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F144">
-        <v>701</v>
+        <v>437</v>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t xml:space="preserve">311274934</t>
+          <t xml:space="preserve">311288314</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-09-25</t>
+          <t xml:space="preserve">2027-12-12</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -7236,20 +7236,20 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t xml:space="preserve">30</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F145">
-        <v>1903</v>
+        <v>6222</v>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t xml:space="preserve">311276907</t>
+          <t xml:space="preserve">311288292</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-10-05</t>
+          <t xml:space="preserve">2027-12-12</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -7286,20 +7286,20 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t xml:space="preserve">31</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F146">
-        <v>410</v>
+        <v>739</v>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t xml:space="preserve">311276907</t>
+          <t xml:space="preserve">311288299</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-10-05</t>
+          <t xml:space="preserve">2027-12-12</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -7331,25 +7331,25 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t xml:space="preserve">9441948</t>
+          <t xml:space="preserve">8899482</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F147">
-        <v>445</v>
+        <v>252</v>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t xml:space="preserve">311280025</t>
+          <t xml:space="preserve">311288301</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-10-23</t>
+          <t xml:space="preserve">2027-12-12</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -7381,25 +7381,25 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t xml:space="preserve">8899384</t>
+          <t xml:space="preserve">8899482</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">30</t>
         </is>
       </c>
       <c r="F148">
-        <v>1476</v>
+        <v>1903</v>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t xml:space="preserve">311283220</t>
+          <t xml:space="preserve">311288301</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-11-10</t>
+          <t xml:space="preserve">2027-12-12</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -7431,25 +7431,25 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t xml:space="preserve">8899384</t>
+          <t xml:space="preserve">8899482</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">31</t>
         </is>
       </c>
       <c r="F149">
-        <v>260</v>
+        <v>410</v>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t xml:space="preserve">311283218</t>
+          <t xml:space="preserve">311288301</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-11-10</t>
+          <t xml:space="preserve">2027-12-12</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -7481,25 +7481,25 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t xml:space="preserve">8899384</t>
+          <t xml:space="preserve">8899482</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F150">
-        <v>5926</v>
+        <v>434</v>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t xml:space="preserve">311283462</t>
+          <t xml:space="preserve">311288301</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-11-13</t>
+          <t xml:space="preserve">2027-12-12</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -7531,25 +7531,25 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t xml:space="preserve">5575145</t>
+          <t xml:space="preserve">8899482</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F151">
-        <v>337</v>
+        <v>1260</v>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t xml:space="preserve">311284088</t>
+          <t xml:space="preserve">311288301</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-11-16</t>
+          <t xml:space="preserve">2027-12-12</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -7581,25 +7581,25 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t xml:space="preserve">5575376</t>
+          <t xml:space="preserve">8899482</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="F152">
-        <v>590</v>
+        <v>1969</v>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t xml:space="preserve">311285478</t>
+          <t xml:space="preserve">311288786</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-11-23</t>
+          <t xml:space="preserve">2027-12-14</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -7631,25 +7631,25 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t xml:space="preserve">4508315</t>
+          <t xml:space="preserve">8899482</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F153">
-        <v>437</v>
+        <v>804</v>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t xml:space="preserve">311288314</t>
+          <t xml:space="preserve">311289322</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-12</t>
+          <t xml:space="preserve">2027-12-18</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -7681,25 +7681,25 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t xml:space="preserve">8899482</t>
+          <t xml:space="preserve">5575936</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F154">
-        <v>6222</v>
+        <v>4596</v>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t xml:space="preserve">311288292</t>
+          <t xml:space="preserve">311289957</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-12</t>
+          <t xml:space="preserve">2027-12-21</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -7731,25 +7731,25 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t xml:space="preserve">8899482</t>
+          <t xml:space="preserve">5581148</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="F155">
-        <v>739</v>
+        <v>360</v>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t xml:space="preserve">311288299</t>
+          <t xml:space="preserve">311346280</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-12</t>
+          <t xml:space="preserve">2028-11-12</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -7781,25 +7781,25 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t xml:space="preserve">8899482</t>
+          <t xml:space="preserve">5579371</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F156">
-        <v>1969</v>
+        <v>974</v>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t xml:space="preserve">311288786</t>
+          <t xml:space="preserve">311347567</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-14</t>
+          <t xml:space="preserve">2028-11-19</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -7831,25 +7831,25 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t xml:space="preserve">8899482</t>
+          <t xml:space="preserve">5580471</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F157">
-        <v>804</v>
+        <v>674</v>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t xml:space="preserve">311289322</t>
+          <t xml:space="preserve">311347531</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-18</t>
+          <t xml:space="preserve">2028-11-19</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -7881,25 +7881,25 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t xml:space="preserve">5575936</t>
+          <t xml:space="preserve">100011734</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F158">
-        <v>4596</v>
+        <v>403</v>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t xml:space="preserve">311289957</t>
+          <t xml:space="preserve">311458075</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-21</t>
+          <t xml:space="preserve">2030-09-01</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -7931,25 +7931,25 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t xml:space="preserve">5581148</t>
+          <t xml:space="preserve">100011734</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F159">
-        <v>360</v>
+        <v>1116</v>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t xml:space="preserve">311346281</t>
+          <t xml:space="preserve">311458304</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-11-12</t>
+          <t xml:space="preserve">2030-09-02</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -7981,7 +7981,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t xml:space="preserve">5579371</t>
+          <t xml:space="preserve">8899386</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -7990,16 +7990,16 @@
         </is>
       </c>
       <c r="F160">
-        <v>974</v>
+        <v>607</v>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t xml:space="preserve">311347567</t>
+          <t xml:space="preserve">311464353</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-11-19</t>
+          <t xml:space="preserve">2030-09-30</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -8031,25 +8031,25 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t xml:space="preserve">5580471</t>
+          <t xml:space="preserve">8899386</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F161">
-        <v>674</v>
+        <v>378</v>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t xml:space="preserve">311347531</t>
+          <t xml:space="preserve">311464353</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-11-19</t>
+          <t xml:space="preserve">2030-09-30</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -8081,25 +8081,25 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t xml:space="preserve">100011734</t>
+          <t xml:space="preserve">8899386</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F162">
-        <v>403</v>
+        <v>378</v>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t xml:space="preserve">311458075</t>
+          <t xml:space="preserve">311464353</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-09-01</t>
+          <t xml:space="preserve">2030-09-30</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -8131,25 +8131,25 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t xml:space="preserve">100011734</t>
+          <t xml:space="preserve">5580961</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F163">
-        <v>1116</v>
+        <v>1408</v>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t xml:space="preserve">311458304</t>
+          <t xml:space="preserve">311468503</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-09-02</t>
+          <t xml:space="preserve">2030-10-21</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -8181,25 +8181,25 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t xml:space="preserve">8899386</t>
+          <t xml:space="preserve">4075942</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F164">
-        <v>607</v>
+        <v>855</v>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t xml:space="preserve">311464353</t>
+          <t xml:space="preserve">311483171</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-09-30</t>
+          <t xml:space="preserve">2030-12-16</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -8231,7 +8231,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t xml:space="preserve">8899386</t>
+          <t xml:space="preserve">4075942</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -8240,16 +8240,16 @@
         </is>
       </c>
       <c r="F165">
-        <v>378</v>
+        <v>324</v>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t xml:space="preserve">311464353</t>
+          <t xml:space="preserve">311483170</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-09-30</t>
+          <t xml:space="preserve">2030-12-16</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -8281,25 +8281,25 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t xml:space="preserve">8899386</t>
+          <t xml:space="preserve">10108979</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F166">
-        <v>378</v>
+        <v>1651</v>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t xml:space="preserve">311464353</t>
+          <t xml:space="preserve">311495820</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-09-30</t>
+          <t xml:space="preserve">2031-02-16</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -8331,7 +8331,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t xml:space="preserve">5580961</t>
+          <t xml:space="preserve">5582681</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -8340,16 +8340,16 @@
         </is>
       </c>
       <c r="F167">
-        <v>1408</v>
+        <v>1436</v>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t xml:space="preserve">311468503</t>
+          <t xml:space="preserve">311497320</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-10-21</t>
+          <t xml:space="preserve">2031-02-22</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -8381,25 +8381,25 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t xml:space="preserve">4075942</t>
+          <t xml:space="preserve">5581565</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F168">
-        <v>855</v>
+        <v>1178</v>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t xml:space="preserve">311483171</t>
+          <t xml:space="preserve">311498972</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-16</t>
+          <t xml:space="preserve">2031-02-26</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -8431,25 +8431,25 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t xml:space="preserve">4075942</t>
+          <t xml:space="preserve">4062718</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F169">
-        <v>324</v>
+        <v>3914</v>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t xml:space="preserve">311483170</t>
+          <t xml:space="preserve">311503309</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-16</t>
+          <t xml:space="preserve">2031-03-15</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -8481,25 +8481,25 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t xml:space="preserve">10108979</t>
+          <t xml:space="preserve">1803393</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F170">
-        <v>1651</v>
+        <v>360</v>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t xml:space="preserve">311495820</t>
+          <t xml:space="preserve">311505041</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-02-16</t>
+          <t xml:space="preserve">2031-03-19</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -8531,25 +8531,25 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t xml:space="preserve">5582681</t>
+          <t xml:space="preserve">8116502</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F171">
-        <v>1436</v>
+        <v>403</v>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t xml:space="preserve">311497320</t>
+          <t xml:space="preserve">311506012</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-02-22</t>
+          <t xml:space="preserve">2031-03-23</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -8581,25 +8581,25 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t xml:space="preserve">5581565</t>
+          <t xml:space="preserve">7893354</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F172">
-        <v>1178</v>
+        <v>380</v>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t xml:space="preserve">311498972</t>
+          <t xml:space="preserve">311510560</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-02-26</t>
+          <t xml:space="preserve">2031-04-07</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -8631,25 +8631,25 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t xml:space="preserve">4062718</t>
+          <t xml:space="preserve">7893354</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F173">
-        <v>3914</v>
+        <v>970</v>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t xml:space="preserve">311503309</t>
+          <t xml:space="preserve">311510570</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-03-15</t>
+          <t xml:space="preserve">2031-04-07</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -8681,25 +8681,25 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t xml:space="preserve">1803393</t>
+          <t xml:space="preserve">9119581</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F174">
-        <v>360</v>
+        <v>1178</v>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t xml:space="preserve">311505041</t>
+          <t xml:space="preserve">311542226</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-03-19</t>
+          <t xml:space="preserve">2031-08-20</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -8731,25 +8731,25 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t xml:space="preserve">8116502</t>
+          <t xml:space="preserve">9119581</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F175">
-        <v>403</v>
+        <v>538</v>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t xml:space="preserve">311506012</t>
+          <t xml:space="preserve">311542226</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-03-23</t>
+          <t xml:space="preserve">2031-08-20</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -8781,25 +8781,25 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t xml:space="preserve">7893354</t>
+          <t xml:space="preserve">9119581</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F176">
-        <v>380</v>
+        <v>1632</v>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t xml:space="preserve">311510560</t>
+          <t xml:space="preserve">311542226</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-04-07</t>
+          <t xml:space="preserve">2031-08-20</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -8831,25 +8831,25 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t xml:space="preserve">7893354</t>
+          <t xml:space="preserve">9119581</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F177">
-        <v>970</v>
+        <v>1483</v>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t xml:space="preserve">311510570</t>
+          <t xml:space="preserve">311542226</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-04-07</t>
+          <t xml:space="preserve">2031-08-20</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -8886,11 +8886,11 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F178">
-        <v>1178</v>
+        <v>388</v>
       </c>
       <c r="G178" t="inlineStr">
         <is>
@@ -8931,25 +8931,25 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t xml:space="preserve">9119581</t>
+          <t xml:space="preserve">5575466</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F179">
-        <v>538</v>
+        <v>4897</v>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t xml:space="preserve">311542226</t>
+          <t xml:space="preserve">311564028</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-20</t>
+          <t xml:space="preserve">2031-11-24</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -8981,25 +8981,25 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t xml:space="preserve">9119581</t>
+          <t xml:space="preserve">9524001</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F180">
-        <v>1632</v>
+        <v>875</v>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t xml:space="preserve">311542226</t>
+          <t xml:space="preserve">311571055</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-20</t>
+          <t xml:space="preserve">2032-01-06</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -9031,25 +9031,25 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t xml:space="preserve">9119581</t>
+          <t xml:space="preserve">5575466</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F181">
-        <v>1483</v>
+        <v>5186</v>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t xml:space="preserve">311542226</t>
+          <t xml:space="preserve">311573049</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-20</t>
+          <t xml:space="preserve">2032-01-18</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -9081,25 +9081,25 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t xml:space="preserve">9119581</t>
+          <t xml:space="preserve">5575466</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F182">
-        <v>388</v>
+        <v>2584</v>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t xml:space="preserve">311542226</t>
+          <t xml:space="preserve">311573049</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-20</t>
+          <t xml:space="preserve">2032-01-18</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
@@ -9131,25 +9131,25 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t xml:space="preserve">5575466</t>
+          <t xml:space="preserve">4508315</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F183">
-        <v>4897</v>
+        <v>1532</v>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t xml:space="preserve">311564028</t>
+          <t xml:space="preserve">311575593</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-11-24</t>
+          <t xml:space="preserve">2032-01-31</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -9181,7 +9181,7 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t xml:space="preserve">9524001</t>
+          <t xml:space="preserve">4508315</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
@@ -9190,16 +9190,16 @@
         </is>
       </c>
       <c r="F184">
-        <v>875</v>
+        <v>1230</v>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t xml:space="preserve">311571055</t>
+          <t xml:space="preserve">311575922</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-01-06</t>
+          <t xml:space="preserve">2032-02-01</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -9231,7 +9231,7 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t xml:space="preserve">5575466</t>
+          <t xml:space="preserve">8747981</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -9240,16 +9240,16 @@
         </is>
       </c>
       <c r="F185">
-        <v>5186</v>
+        <v>369</v>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t xml:space="preserve">311573049</t>
+          <t xml:space="preserve">311578920</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-01-18</t>
+          <t xml:space="preserve">2032-02-15</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -9281,25 +9281,25 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t xml:space="preserve">5575466</t>
+          <t xml:space="preserve">5581674</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="F186">
-        <v>2584</v>
+        <v>709</v>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t xml:space="preserve">311573049</t>
+          <t xml:space="preserve">311585347</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-01-18</t>
+          <t xml:space="preserve">2032-03-15</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -9331,25 +9331,25 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t xml:space="preserve">4508315</t>
+          <t xml:space="preserve">5581674</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="F187">
-        <v>1532</v>
+        <v>284</v>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t xml:space="preserve">311575593</t>
+          <t xml:space="preserve">311585347</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-01-31</t>
+          <t xml:space="preserve">2032-03-15</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -9381,25 +9381,25 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t xml:space="preserve">4508315</t>
+          <t xml:space="preserve">5581674</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F188">
-        <v>1230</v>
+        <v>536</v>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t xml:space="preserve">311575922</t>
+          <t xml:space="preserve">311585347</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-02-01</t>
+          <t xml:space="preserve">2032-03-15</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -9436,15 +9436,15 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F189">
-        <v>709</v>
+        <v>616</v>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t xml:space="preserve">311585352</t>
+          <t xml:space="preserve">311585347</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -9494,7 +9494,7 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t xml:space="preserve">311585357</t>
+          <t xml:space="preserve">311585347</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -9544,7 +9544,7 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t xml:space="preserve">311585356</t>
+          <t xml:space="preserve">311585347</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -9581,25 +9581,25 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t xml:space="preserve">381665, 381666</t>
+          <t xml:space="preserve">5581674</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F192">
-        <v>844</v>
+        <v>260</v>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t xml:space="preserve">311594036</t>
+          <t xml:space="preserve">311585347</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-04-21</t>
+          <t xml:space="preserve">2032-03-15</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -10694,12 +10694,12 @@
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t xml:space="preserve">311881368</t>
+          <t xml:space="preserve">311881460</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-02-10</t>
+          <t xml:space="preserve">2036-02-11</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">

--- a/public/exports/29189579.xlsx
+++ b/public/exports/29189579.xlsx
@@ -91,26 +91,26 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Birkevej 2</t>
+          <t xml:space="preserve">Bilstrupvej 28A</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7860</t>
+          <t xml:space="preserve">7800</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100007822</t>
+          <t xml:space="preserve">5581093</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H2">
-        <v>273</v>
+        <v>496</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -151,7 +151,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vejbyvej 5A</t>
+          <t xml:space="preserve">Birkevej 2</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -166,11 +166,11 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="H3">
-        <v>1612</v>
+        <v>273</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -211,26 +211,26 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyrovej 5</t>
+          <t xml:space="preserve">Blomstervejen 30</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">7800</t>
+          <t xml:space="preserve">7840</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve">100672194</t>
+          <t xml:space="preserve">9961833</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H4">
-        <v>563</v>
+        <v>593</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -271,26 +271,26 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hjaltesvej 3B</t>
+          <t xml:space="preserve">Bredgade 51</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">7800</t>
+          <t xml:space="preserve">7870</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">380711, 380712</t>
+          <t xml:space="preserve">8184585</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H5">
-        <v>1290</v>
+        <v>1006</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -331,7 +331,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hjaltesvej 3A</t>
+          <t xml:space="preserve">Brårupgade 15C</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -341,16 +341,16 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">380711, 380712</t>
+          <t xml:space="preserve">5575834</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H6">
-        <v>791</v>
+        <v>513</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -391,7 +391,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hjaltesvej 7A</t>
+          <t xml:space="preserve">Brårupvej 94</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -401,16 +401,16 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">380712</t>
+          <t xml:space="preserve">5580769</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H7">
-        <v>414</v>
+        <v>388</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -451,7 +451,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Egerisvej 12</t>
+          <t xml:space="preserve">Brårupvej 94</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -461,16 +461,16 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">381206, 381207</t>
+          <t xml:space="preserve">5582112</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="H8">
-        <v>1717</v>
+        <v>1112</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -511,26 +511,26 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadion Alle 3</t>
+          <t xml:space="preserve">Brårupvej 94</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">7860</t>
+          <t xml:space="preserve">7800</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve">381215, 381216</t>
+          <t xml:space="preserve">5582112</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="H9">
-        <v>3975</v>
+        <v>748</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -571,7 +571,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Præstevejen 28</t>
+          <t xml:space="preserve">Brårupvej 94</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -581,16 +581,16 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t xml:space="preserve">381665, 381666</t>
+          <t xml:space="preserve">5582112</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="H10">
-        <v>844</v>
+        <v>1496</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -631,7 +631,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parcelvej 14</t>
+          <t xml:space="preserve">Brårupvej 94</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -641,16 +641,16 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t xml:space="preserve">382049, 382050</t>
+          <t xml:space="preserve">5582112</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="H11">
-        <v>579</v>
+        <v>584</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -691,7 +691,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parcelvej 30</t>
+          <t xml:space="preserve">Brårupvej 94</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -701,16 +701,16 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t xml:space="preserve">382050</t>
+          <t xml:space="preserve">5582112</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="H12">
-        <v>403</v>
+        <v>593</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -751,7 +751,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thinggade 15</t>
+          <t xml:space="preserve">Brårupvej 94</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -761,16 +761,16 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t xml:space="preserve">382557, 382558, 382559</t>
+          <t xml:space="preserve">5582112</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="H13">
-        <v>1019</v>
+        <v>304</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -811,26 +811,26 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 13A</t>
+          <t xml:space="preserve">Brårupvej 94</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">7840</t>
+          <t xml:space="preserve">7800</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t xml:space="preserve">4050055</t>
+          <t xml:space="preserve">5582112</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H14">
-        <v>337</v>
+        <v>912</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -871,17 +871,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 13</t>
+          <t xml:space="preserve">Brårupvej 94</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">7840</t>
+          <t xml:space="preserve">7800</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t xml:space="preserve">4050055</t>
+          <t xml:space="preserve">5582112</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -890,7 +890,7 @@
         </is>
       </c>
       <c r="H15">
-        <v>740</v>
+        <v>1268</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -931,26 +931,26 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 11C</t>
+          <t xml:space="preserve">Brårupvej 94</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">7840</t>
+          <t xml:space="preserve">7800</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t xml:space="preserve">4050055</t>
+          <t xml:space="preserve">5582112</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H16">
-        <v>1219</v>
+        <v>285</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -991,26 +991,26 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sdr. Allé 1</t>
+          <t xml:space="preserve">Brårupvej 94</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">7870</t>
+          <t xml:space="preserve">7800</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t xml:space="preserve">4058695</t>
+          <t xml:space="preserve">5582112</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H17">
-        <v>2067</v>
+        <v>340</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1051,26 +1051,26 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jenlevej 6</t>
+          <t xml:space="preserve">Brårupvej 94</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">7870</t>
+          <t xml:space="preserve">7800</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t xml:space="preserve">4059356</t>
+          <t xml:space="preserve">5582112</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t xml:space="preserve">44</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="H18">
-        <v>256</v>
+        <v>754</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1111,26 +1111,26 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søndergade 20</t>
+          <t xml:space="preserve">Dalgas Alle 24</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">7870</t>
+          <t xml:space="preserve">7800</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t xml:space="preserve">4060423</t>
+          <t xml:space="preserve">5581102</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H19">
-        <v>6657</v>
+        <v>1040</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1291,26 +1291,26 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tingagervej 2</t>
+          <t xml:space="preserve">Flyvej 18A</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t xml:space="preserve">7884</t>
+          <t xml:space="preserve">7800</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t xml:space="preserve">4066849</t>
+          <t xml:space="preserve">748334, 5580236</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H22">
-        <v>665</v>
+        <v>1267</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1351,17 +1351,17 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Æblevej 2</t>
+          <t xml:space="preserve">Folmentoftvej 2</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t xml:space="preserve">7870</t>
+          <t xml:space="preserve">7800</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t xml:space="preserve">4070705</t>
+          <t xml:space="preserve">748337, 4508603</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1370,7 +1370,7 @@
         </is>
       </c>
       <c r="H23">
-        <v>2564</v>
+        <v>277</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1411,26 +1411,26 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ålbækvej 16A</t>
+          <t xml:space="preserve">Frederiksgade 21K</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t xml:space="preserve">7860</t>
+          <t xml:space="preserve">7800</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t xml:space="preserve">4074902</t>
+          <t xml:space="preserve">5575936</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H24">
-        <v>743</v>
+        <v>428</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Strandvejen 28</t>
+          <t xml:space="preserve">Frederiksgade 21K</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1481,16 +1481,16 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t xml:space="preserve">500024, 500025, 100014875, 500026</t>
+          <t xml:space="preserve">5575936</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H25">
-        <v>2946</v>
+        <v>1377</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Theaterpladsen 10</t>
+          <t xml:space="preserve">Frederiksgade 21K</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1541,16 +1541,16 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t xml:space="preserve">5575087</t>
+          <t xml:space="preserve">5575936</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H26">
-        <v>1072</v>
+        <v>418</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1591,7 +1591,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Møllegade 5</t>
+          <t xml:space="preserve">Frejasvej 34</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1601,16 +1601,16 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t xml:space="preserve">5575173</t>
+          <t xml:space="preserve">8395726</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H27">
-        <v>3510</v>
+        <v>404</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -1651,7 +1651,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brårupgade 15C</t>
+          <t xml:space="preserve">Frugtparken 15</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1661,16 +1661,16 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t xml:space="preserve">5575834</t>
+          <t xml:space="preserve">748322, 9012346</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H28">
-        <v>513</v>
+        <v>525</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -1711,7 +1711,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frederiksgade 21K</t>
+          <t xml:space="preserve">Gefionsvej 19</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1721,16 +1721,16 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t xml:space="preserve">5575936</t>
+          <t xml:space="preserve">8268606</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H29">
-        <v>428</v>
+        <v>417</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frederiksgade 21K</t>
+          <t xml:space="preserve">Gefionsvej 24</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1781,16 +1781,16 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t xml:space="preserve">5575936</t>
+          <t xml:space="preserve">5582842</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H30">
-        <v>1377</v>
+        <v>984</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frederiksgade 21K</t>
+          <t xml:space="preserve">Gefionsvej 29</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1841,16 +1841,16 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t xml:space="preserve">5575936</t>
+          <t xml:space="preserve">8268606</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H31">
-        <v>418</v>
+        <v>300</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -1891,26 +1891,26 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hjalmar Kjems Allé 5A</t>
+          <t xml:space="preserve">Greenlab 10</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t xml:space="preserve">7800</t>
+          <t xml:space="preserve">7860</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t xml:space="preserve">5578173</t>
+          <t xml:space="preserve">748320, 9376480</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H32">
-        <v>813</v>
+        <v>280</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -1951,7 +1951,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hjalmar Kjems Allé 7A</t>
+          <t xml:space="preserve">Gyrovej 5</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1961,16 +1961,16 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t xml:space="preserve">5578173</t>
+          <t xml:space="preserve">100672194</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H33">
-        <v>531</v>
+        <v>563</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kompagnigade 26</t>
+          <t xml:space="preserve">Havnevej 38</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2021,7 +2021,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t xml:space="preserve">5578628</t>
+          <t xml:space="preserve">748085, 5579377</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2030,7 +2030,7 @@
         </is>
       </c>
       <c r="H34">
-        <v>466</v>
+        <v>1732</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -2071,7 +2071,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Strandvejen 24A</t>
+          <t xml:space="preserve">Havnevej 47</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2081,16 +2081,16 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t xml:space="preserve">5579321</t>
+          <t xml:space="preserve">748336, 8899388</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="H35">
-        <v>509</v>
+        <v>490</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mejsevej 12</t>
+          <t xml:space="preserve">Havnevej 57</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t xml:space="preserve">5579425</t>
+          <t xml:space="preserve">748079, 5579359</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2150,7 +2150,7 @@
         </is>
       </c>
       <c r="H36">
-        <v>283</v>
+        <v>680</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -2191,7 +2191,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skyttevej 14</t>
+          <t xml:space="preserve">Havnevej 57</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2201,16 +2201,16 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t xml:space="preserve">5579990</t>
+          <t xml:space="preserve">748079, 5579359</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H37">
-        <v>9077</v>
+        <v>700</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brårupvej 94</t>
+          <t xml:space="preserve">Havnevej 57</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2261,16 +2261,16 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t xml:space="preserve">5580769</t>
+          <t xml:space="preserve">748079, 5579359</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H38">
-        <v>388</v>
+        <v>866</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -2311,7 +2311,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bilstrupvej 28A</t>
+          <t xml:space="preserve">Hjalmar Kjems Allé 5A</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t xml:space="preserve">5581093</t>
+          <t xml:space="preserve">5578173</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2330,7 +2330,7 @@
         </is>
       </c>
       <c r="H39">
-        <v>496</v>
+        <v>813</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -2371,7 +2371,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dalgas Alle 24</t>
+          <t xml:space="preserve">Hjalmar Kjems Allé 7A</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2381,16 +2381,16 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t xml:space="preserve">5581102</t>
+          <t xml:space="preserve">5578173</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H40">
-        <v>1040</v>
+        <v>531</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brårupvej 94</t>
+          <t xml:space="preserve">Hjaltesvej 3A</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2441,16 +2441,16 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t xml:space="preserve">5582112</t>
+          <t xml:space="preserve">380711, 380712</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H41">
-        <v>1112</v>
+        <v>791</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -2491,7 +2491,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brårupvej 94</t>
+          <t xml:space="preserve">Hjaltesvej 3B</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2501,16 +2501,16 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t xml:space="preserve">5582112</t>
+          <t xml:space="preserve">380711, 380712</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H42">
-        <v>748</v>
+        <v>1290</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -2551,26 +2551,26 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brårupvej 94</t>
+          <t xml:space="preserve">Hostrupvej 13</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t xml:space="preserve">7800</t>
+          <t xml:space="preserve">7860</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t xml:space="preserve">5582112</t>
+          <t xml:space="preserve">9875681</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H43">
-        <v>1496</v>
+        <v>1806</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -2611,26 +2611,26 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brårupvej 94</t>
+          <t xml:space="preserve">Jenlevej 6</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t xml:space="preserve">7800</t>
+          <t xml:space="preserve">7870</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t xml:space="preserve">5582112</t>
+          <t xml:space="preserve">4059356</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">44</t>
         </is>
       </c>
       <c r="H44">
-        <v>584</v>
+        <v>256</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -2671,7 +2671,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brårupvej 94</t>
+          <t xml:space="preserve">Killesmosevej 1</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2681,16 +2681,16 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t xml:space="preserve">5582112</t>
+          <t xml:space="preserve">748266, 100075804</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H45">
-        <v>593</v>
+        <v>682</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -2731,7 +2731,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brårupvej 94</t>
+          <t xml:space="preserve">Kirke Alle 3</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2746,11 +2746,11 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">24</t>
         </is>
       </c>
       <c r="H46">
-        <v>304</v>
+        <v>1507</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -2791,7 +2791,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirke Alle 3</t>
+          <t xml:space="preserve">Kirke Alle 5</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2806,11 +2806,11 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t xml:space="preserve">24</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="H47">
-        <v>1507</v>
+        <v>336</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -2851,7 +2851,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brårupvej 94</t>
+          <t xml:space="preserve">Kompagnigade 26</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2861,16 +2861,16 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t xml:space="preserve">5582112</t>
+          <t xml:space="preserve">5578628</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H48">
-        <v>912</v>
+        <v>466</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -2911,7 +2911,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brårupvej 94</t>
+          <t xml:space="preserve">Krabbesholm Alle 2</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -2921,16 +2921,16 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t xml:space="preserve">5582112</t>
+          <t xml:space="preserve">748075, 5579184</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H49">
-        <v>1268</v>
+        <v>1673</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -2971,26 +2971,26 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brårupvej 94</t>
+          <t xml:space="preserve">Lufthavnsvej 7</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t xml:space="preserve">7800</t>
+          <t xml:space="preserve">7840</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t xml:space="preserve">5582112</t>
+          <t xml:space="preserve">748323, 4049713</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H50">
-        <v>285</v>
+        <v>306</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brårupvej 94</t>
+          <t xml:space="preserve">Marienlystvej 11</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3041,16 +3041,16 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t xml:space="preserve">5582112</t>
+          <t xml:space="preserve">5584332</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H51">
-        <v>340</v>
+        <v>9131</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -3091,7 +3091,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirke Alle 5</t>
+          <t xml:space="preserve">Mejsevej 12</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3101,16 +3101,16 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t xml:space="preserve">5582112</t>
+          <t xml:space="preserve">5579425</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H52">
-        <v>336</v>
+        <v>283</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
@@ -3151,7 +3151,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brårupvej 94</t>
+          <t xml:space="preserve">Mejsevej 1A</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3161,16 +3161,16 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t xml:space="preserve">5582112</t>
+          <t xml:space="preserve">7046491</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H53">
-        <v>754</v>
+        <v>809</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
@@ -3211,7 +3211,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gefionsvej 24</t>
+          <t xml:space="preserve">Møllegade 5</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3221,16 +3221,16 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t xml:space="preserve">5582842</t>
+          <t xml:space="preserve">5575173</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H54">
-        <v>984</v>
+        <v>3510</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
@@ -3271,7 +3271,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Marienlystvej 11</t>
+          <t xml:space="preserve">Nordhavnsvej 8</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3281,16 +3281,16 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t xml:space="preserve">5584332</t>
+          <t xml:space="preserve">748077, 5579353</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H55">
-        <v>9131</v>
+        <v>748</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
@@ -3331,26 +3331,26 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mejsevej 1A</t>
+          <t xml:space="preserve">Næstildvej 10A</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t xml:space="preserve">7800</t>
+          <t xml:space="preserve">7860</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t xml:space="preserve">7046491</t>
+          <t xml:space="preserve">8882814, 100623370</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H56">
-        <v>809</v>
+        <v>445</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
@@ -3391,17 +3391,17 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Krabbesholm Alle 2</t>
+          <t xml:space="preserve">Næstildvej 2</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t xml:space="preserve">7800</t>
+          <t xml:space="preserve">7860</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t xml:space="preserve">748075, 5579184</t>
+          <t xml:space="preserve">9391734</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -3410,7 +3410,7 @@
         </is>
       </c>
       <c r="H57">
-        <v>1673</v>
+        <v>1776</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
@@ -3451,7 +3451,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nordhavnsvej 8</t>
+          <t xml:space="preserve">Parcelvej 14</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t xml:space="preserve">748077, 5579353</t>
+          <t xml:space="preserve">382049, 382050</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -3470,7 +3470,7 @@
         </is>
       </c>
       <c r="H58">
-        <v>748</v>
+        <v>579</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Havnevej 57</t>
+          <t xml:space="preserve">Parcelvej 30</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -3521,16 +3521,16 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t xml:space="preserve">748079, 5579359</t>
+          <t xml:space="preserve">382050</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H59">
-        <v>680</v>
+        <v>403</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
@@ -3571,26 +3571,26 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Havnevej 57</t>
+          <t xml:space="preserve">Sandkrogen 10B</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t xml:space="preserve">7800</t>
+          <t xml:space="preserve">7840</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t xml:space="preserve">748079, 5579359</t>
+          <t xml:space="preserve">748332, 9524232</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H60">
-        <v>700</v>
+        <v>293</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
@@ -3631,26 +3631,26 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Havnevej 57</t>
+          <t xml:space="preserve">Sdr. Allé 1</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t xml:space="preserve">7800</t>
+          <t xml:space="preserve">7870</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t xml:space="preserve">748079, 5579359</t>
+          <t xml:space="preserve">4058695</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H61">
-        <v>866</v>
+        <v>2067</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
@@ -3691,17 +3691,17 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Strandvejen 4</t>
+          <t xml:space="preserve">Skivevej 13</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t xml:space="preserve">7800</t>
+          <t xml:space="preserve">7860</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t xml:space="preserve">748081, 5579361</t>
+          <t xml:space="preserve">8798252</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -3710,7 +3710,7 @@
         </is>
       </c>
       <c r="H62">
-        <v>1152</v>
+        <v>2716</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -3751,26 +3751,26 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Strandvejen 6</t>
+          <t xml:space="preserve">Skolevej 11C</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t xml:space="preserve">7800</t>
+          <t xml:space="preserve">7840</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t xml:space="preserve">748082, 5579362</t>
+          <t xml:space="preserve">4050055</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H63">
-        <v>2229</v>
+        <v>1219</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
@@ -3811,26 +3811,26 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Havnevej 38</t>
+          <t xml:space="preserve">Skolevej 13</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t xml:space="preserve">7800</t>
+          <t xml:space="preserve">7840</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t xml:space="preserve">748085, 5579377</t>
+          <t xml:space="preserve">4050055</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H64">
-        <v>1732</v>
+        <v>740</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
@@ -3871,26 +3871,26 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Strandvejen 3A</t>
+          <t xml:space="preserve">Skolevej 13A</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t xml:space="preserve">7800</t>
+          <t xml:space="preserve">7840</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t xml:space="preserve">748090, 5579318</t>
+          <t xml:space="preserve">4050055</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H65">
-        <v>574</v>
+        <v>337</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
@@ -3931,7 +3931,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Strandvejen 18</t>
+          <t xml:space="preserve">Skyttevej 14</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -3941,16 +3941,16 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t xml:space="preserve">748091, 100013151</t>
+          <t xml:space="preserve">5579990</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H66">
-        <v>889</v>
+        <v>9077</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
@@ -3991,17 +3991,17 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stenøre 18B</t>
+          <t xml:space="preserve">Stadion Alle 3</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t xml:space="preserve">7884</t>
+          <t xml:space="preserve">7860</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t xml:space="preserve">748145, 4066935</t>
+          <t xml:space="preserve">381215, 381216</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -4010,7 +4010,7 @@
         </is>
       </c>
       <c r="H67">
-        <v>287</v>
+        <v>3975</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
@@ -4051,17 +4051,17 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Killesmosevej 1</t>
+          <t xml:space="preserve">Stensbjergvej 2</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t xml:space="preserve">7800</t>
+          <t xml:space="preserve">7840</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t xml:space="preserve">748266, 100075804</t>
+          <t xml:space="preserve">748327, 4049692</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -4070,7 +4070,7 @@
         </is>
       </c>
       <c r="H68">
-        <v>682</v>
+        <v>289</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
@@ -4111,26 +4111,26 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Viumvej 6</t>
+          <t xml:space="preserve">Stenøre 18B</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t xml:space="preserve">7870</t>
+          <t xml:space="preserve">7884</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t xml:space="preserve">748295, 7382442</t>
+          <t xml:space="preserve">748145, 4066935</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H69">
-        <v>447</v>
+        <v>287</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
@@ -4171,26 +4171,26 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Greenlab 10</t>
+          <t xml:space="preserve">Stoholmvej 22</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t xml:space="preserve">7860</t>
+          <t xml:space="preserve">7840</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t xml:space="preserve">748320, 9376480</t>
+          <t xml:space="preserve">8116502</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="H70">
-        <v>280</v>
+        <v>496</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
@@ -4231,26 +4231,26 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frugtparken 15</t>
+          <t xml:space="preserve">Stoholmvej 24C</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t xml:space="preserve">7800</t>
+          <t xml:space="preserve">7840</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t xml:space="preserve">748322, 9012346</t>
+          <t xml:space="preserve">8116502</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="H71">
-        <v>525</v>
+        <v>392</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
@@ -4291,17 +4291,17 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lufthavnsvej 7</t>
+          <t xml:space="preserve">Strandvejen 16</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t xml:space="preserve">7840</t>
+          <t xml:space="preserve">7800</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t xml:space="preserve">748323, 4049713</t>
+          <t xml:space="preserve">748353, 8811417</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -4310,7 +4310,7 @@
         </is>
       </c>
       <c r="H72">
-        <v>306</v>
+        <v>1233</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
@@ -4351,26 +4351,26 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stensbjergvej 2</t>
+          <t xml:space="preserve">Strandvejen 16</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t xml:space="preserve">7840</t>
+          <t xml:space="preserve">7800</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t xml:space="preserve">748327, 4049692</t>
+          <t xml:space="preserve">748353, 8811417</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H73">
-        <v>289</v>
+        <v>10931</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
@@ -4411,26 +4411,26 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sandkrogen 10B</t>
+          <t xml:space="preserve">Strandvejen 18</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t xml:space="preserve">7840</t>
+          <t xml:space="preserve">7800</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t xml:space="preserve">748332, 9524232</t>
+          <t xml:space="preserve">748091, 100013151</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H74">
-        <v>293</v>
+        <v>889</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
@@ -4471,7 +4471,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Flyvej 18A</t>
+          <t xml:space="preserve">Strandvejen 24A</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -4481,16 +4481,16 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t xml:space="preserve">748334, 5580236</t>
+          <t xml:space="preserve">5579321</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H75">
-        <v>1267</v>
+        <v>509</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
@@ -4531,7 +4531,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Havnevej 47</t>
+          <t xml:space="preserve">Strandvejen 28</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -4541,16 +4541,16 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t xml:space="preserve">748336, 8899388</t>
+          <t xml:space="preserve">500024, 500025, 100014875, 500026</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H76">
-        <v>490</v>
+        <v>2946</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
@@ -4591,7 +4591,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Folmentoftvej 2</t>
+          <t xml:space="preserve">Strandvejen 3A</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -4601,7 +4601,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t xml:space="preserve">748337, 4508603</t>
+          <t xml:space="preserve">748090, 5579318</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -4610,7 +4610,7 @@
         </is>
       </c>
       <c r="H77">
-        <v>277</v>
+        <v>574</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
@@ -4651,7 +4651,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Strandvejen 16</t>
+          <t xml:space="preserve">Strandvejen 4</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t xml:space="preserve">748353, 8811417</t>
+          <t xml:space="preserve">748081, 5579361</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -4670,7 +4670,7 @@
         </is>
       </c>
       <c r="H78">
-        <v>1233</v>
+        <v>1152</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
@@ -4711,7 +4711,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Strandvejen 16</t>
+          <t xml:space="preserve">Strandvejen 6</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -4721,16 +4721,16 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t xml:space="preserve">748353, 8811417</t>
+          <t xml:space="preserve">748082, 5579362</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H79">
-        <v>10931</v>
+        <v>2229</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
@@ -4771,7 +4771,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Viumvej 13</t>
+          <t xml:space="preserve">Søndergade 20</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -4781,16 +4781,16 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t xml:space="preserve">748359, 4070602</t>
+          <t xml:space="preserve">4060423</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H80">
-        <v>409</v>
+        <v>6657</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
@@ -4831,17 +4831,17 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østergade 13C</t>
+          <t xml:space="preserve">Theaterpladsen 10</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t xml:space="preserve">7860</t>
+          <t xml:space="preserve">7800</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t xml:space="preserve">7870665</t>
+          <t xml:space="preserve">5575087</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -4850,7 +4850,7 @@
         </is>
       </c>
       <c r="H81">
-        <v>2919</v>
+        <v>1072</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
@@ -4891,26 +4891,26 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stoholmvej 24C</t>
+          <t xml:space="preserve">Tingagervej 2</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t xml:space="preserve">7840</t>
+          <t xml:space="preserve">7884</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t xml:space="preserve">8116502</t>
+          <t xml:space="preserve">4066849</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H82">
-        <v>392</v>
+        <v>665</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
@@ -4951,26 +4951,26 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stoholmvej 22</t>
+          <t xml:space="preserve">Toustrupvej 14</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t xml:space="preserve">7840</t>
+          <t xml:space="preserve">7870</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t xml:space="preserve">8116502</t>
+          <t xml:space="preserve">9681144</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H83">
-        <v>496</v>
+        <v>3176</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
@@ -5011,26 +5011,26 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bredgade 51</t>
+          <t xml:space="preserve">Vejbyvej 5A</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t xml:space="preserve">7870</t>
+          <t xml:space="preserve">7860</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t xml:space="preserve">8184585</t>
+          <t xml:space="preserve">100007822</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H84">
-        <v>1006</v>
+        <v>1612</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
@@ -5071,26 +5071,26 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gefionsvej 19</t>
+          <t xml:space="preserve">Viumvej 13</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t xml:space="preserve">7800</t>
+          <t xml:space="preserve">7870</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t xml:space="preserve">8268606</t>
+          <t xml:space="preserve">748359, 4070602</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H85">
-        <v>417</v>
+        <v>409</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
@@ -5131,17 +5131,17 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gefionsvej 29</t>
+          <t xml:space="preserve">Viumvej 6</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t xml:space="preserve">7800</t>
+          <t xml:space="preserve">7870</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t xml:space="preserve">8268606</t>
+          <t xml:space="preserve">748295, 7382442</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -5150,7 +5150,7 @@
         </is>
       </c>
       <c r="H86">
-        <v>300</v>
+        <v>447</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
@@ -5191,26 +5191,26 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frejasvej 34</t>
+          <t xml:space="preserve">Ålbækvej 16A</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t xml:space="preserve">7800</t>
+          <t xml:space="preserve">7860</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t xml:space="preserve">8395726</t>
+          <t xml:space="preserve">4074902</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H87">
-        <v>404</v>
+        <v>743</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
@@ -5251,17 +5251,17 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skivevej 13</t>
+          <t xml:space="preserve">Æblevej 2</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t xml:space="preserve">7860</t>
+          <t xml:space="preserve">7870</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t xml:space="preserve">8798252</t>
+          <t xml:space="preserve">4070705</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -5270,7 +5270,7 @@
         </is>
       </c>
       <c r="H88">
-        <v>2716</v>
+        <v>2564</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
@@ -5311,7 +5311,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Næstildvej 10A</t>
+          <t xml:space="preserve">Østergade 13C</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -5321,16 +5321,16 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t xml:space="preserve">8882814, 100623370</t>
+          <t xml:space="preserve">7870665</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H89">
-        <v>445</v>
+        <v>2919</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
@@ -5371,17 +5371,17 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Næstildvej 2</t>
+          <t xml:space="preserve">Skivevej 1</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t xml:space="preserve">7860</t>
+          <t xml:space="preserve">7870</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t xml:space="preserve">9391734</t>
+          <t xml:space="preserve">4062734</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -5390,21 +5390,21 @@
         </is>
       </c>
       <c r="H90">
-        <v>1776</v>
+        <v>591</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200015802</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-06-24</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -5431,17 +5431,17 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Toustrupvej 14</t>
+          <t xml:space="preserve">Nattergalevej 1</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t xml:space="preserve">7870</t>
+          <t xml:space="preserve">7800</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t xml:space="preserve">9681144</t>
+          <t xml:space="preserve">9815958</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -5450,21 +5450,21 @@
         </is>
       </c>
       <c r="H91">
-        <v>3176</v>
+        <v>766</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200027486</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2020-02-01</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -5491,40 +5491,40 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hostrupvej 13</t>
+          <t xml:space="preserve">Nattergalevej 11</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t xml:space="preserve">7860</t>
+          <t xml:space="preserve">7800</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t xml:space="preserve">9875681</t>
+          <t xml:space="preserve">9815958</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H92">
-        <v>1806</v>
+        <v>733</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200027494</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2020-02-01</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -5551,40 +5551,40 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Blomstervejen 30</t>
+          <t xml:space="preserve">Nattergalevej 5</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t xml:space="preserve">7840</t>
+          <t xml:space="preserve">7800</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t xml:space="preserve">9961833</t>
+          <t xml:space="preserve">9815958</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H93">
-        <v>593</v>
+        <v>436</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200027518</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2020-02-01</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -5611,35 +5611,35 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skivevej 1</t>
+          <t xml:space="preserve">Nattergalevej 9</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t xml:space="preserve">7870</t>
+          <t xml:space="preserve">7800</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t xml:space="preserve">4062734</t>
+          <t xml:space="preserve">9815958</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H94">
-        <v>591</v>
+        <v>801</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t xml:space="preserve">200015802</t>
+          <t xml:space="preserve">200027494</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-06-24</t>
+          <t xml:space="preserve">2020-02-01</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -5671,7 +5671,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nattergalevej 1</t>
+          <t xml:space="preserve">Nattergalevej 7</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -5686,20 +5686,20 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H95">
-        <v>766</v>
+        <v>296</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t xml:space="preserve">200027494</t>
+          <t xml:space="preserve">200027548</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-02-01</t>
+          <t xml:space="preserve">2020-02-02</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -5731,35 +5731,35 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nattergalevej 5</t>
+          <t xml:space="preserve">Nørre Ramsingvej 21</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t xml:space="preserve">7800</t>
+          <t xml:space="preserve">7860</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t xml:space="preserve">9815958</t>
+          <t xml:space="preserve">4075942</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H96">
-        <v>436</v>
+        <v>1315</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t xml:space="preserve">200027494</t>
+          <t xml:space="preserve">200029108</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-02-01</t>
+          <t xml:space="preserve">2020-03-12</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
@@ -5791,7 +5791,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nattergalevej 9</t>
+          <t xml:space="preserve">Kisumvej 32</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -5801,25 +5801,25 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t xml:space="preserve">9815958</t>
+          <t xml:space="preserve">4508315</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="H97">
-        <v>801</v>
+        <v>1525</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t xml:space="preserve">200027494</t>
+          <t xml:space="preserve">200040147</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-02-01</t>
+          <t xml:space="preserve">2020-11-01</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -5851,7 +5851,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nattergalevej 11</t>
+          <t xml:space="preserve">Rudemøllevej 1</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -5861,25 +5861,25 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t xml:space="preserve">9815958</t>
+          <t xml:space="preserve">4057006</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="H98">
-        <v>733</v>
+        <v>472</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t xml:space="preserve">200027494</t>
+          <t xml:space="preserve">200044236</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-02-01</t>
+          <t xml:space="preserve">2021-01-12</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -5911,7 +5911,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nattergalevej 7</t>
+          <t xml:space="preserve">Rudemøllevej 3</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -5921,25 +5921,25 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t xml:space="preserve">9815958</t>
+          <t xml:space="preserve">4057006</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H99">
-        <v>296</v>
+        <v>481</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t xml:space="preserve">200027548</t>
+          <t xml:space="preserve">200044236</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-02-02</t>
+          <t xml:space="preserve">2021-01-12</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -5971,35 +5971,35 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørre Ramsingvej 21</t>
+          <t xml:space="preserve">Bredgade 51A</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t xml:space="preserve">7860</t>
+          <t xml:space="preserve">7870</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t xml:space="preserve">4075942</t>
+          <t xml:space="preserve">8184584</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H100">
-        <v>1315</v>
+        <v>475</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t xml:space="preserve">200029108</t>
+          <t xml:space="preserve">200045482</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-03-12</t>
+          <t xml:space="preserve">2021-02-10</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -6031,35 +6031,35 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kisumvej 32</t>
+          <t xml:space="preserve">Bredgade 51A</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t xml:space="preserve">7800</t>
+          <t xml:space="preserve">7870</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t xml:space="preserve">4508315</t>
+          <t xml:space="preserve">8184584</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H101">
-        <v>1525</v>
+        <v>452</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t xml:space="preserve">200040147</t>
+          <t xml:space="preserve">200045483</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-11-01</t>
+          <t xml:space="preserve">2021-02-10</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -6091,35 +6091,35 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rudemøllevej 3</t>
+          <t xml:space="preserve">Bredgade 51B</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t xml:space="preserve">7800</t>
+          <t xml:space="preserve">7870</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t xml:space="preserve">4057006</t>
+          <t xml:space="preserve">8184584</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H102">
-        <v>481</v>
+        <v>532</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t xml:space="preserve">200044236</t>
+          <t xml:space="preserve">200045484</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-01-12</t>
+          <t xml:space="preserve">2021-02-10</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
@@ -6151,35 +6151,35 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rudemøllevej 1</t>
+          <t xml:space="preserve">Bredgade 51B</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t xml:space="preserve">7800</t>
+          <t xml:space="preserve">7870</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t xml:space="preserve">4057006</t>
+          <t xml:space="preserve">8184584</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H103">
-        <v>472</v>
+        <v>445</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t xml:space="preserve">200044236</t>
+          <t xml:space="preserve">200045485</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-01-12</t>
+          <t xml:space="preserve">2021-02-10</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
@@ -6211,35 +6211,35 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bredgade 51A</t>
+          <t xml:space="preserve">Ginnerupvej 4</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t xml:space="preserve">7870</t>
+          <t xml:space="preserve">7860</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t xml:space="preserve">8184584</t>
+          <t xml:space="preserve">8798318</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H104">
-        <v>475</v>
+        <v>403</v>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t xml:space="preserve">200045482</t>
+          <t xml:space="preserve">310017203</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-02-10</t>
+          <t xml:space="preserve">2022-12-12</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
@@ -6271,35 +6271,35 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bredgade 51A</t>
+          <t xml:space="preserve">Brårupvej 126</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t xml:space="preserve">7870</t>
+          <t xml:space="preserve">7800</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t xml:space="preserve">8184584</t>
+          <t xml:space="preserve">5580269</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H105">
-        <v>452</v>
+        <v>272</v>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t xml:space="preserve">200045483</t>
+          <t xml:space="preserve">311071797</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-02-10</t>
+          <t xml:space="preserve">2024-09-04</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
@@ -6331,35 +6331,35 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bredgade 51B</t>
+          <t xml:space="preserve">Thinggade 15</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t xml:space="preserve">7870</t>
+          <t xml:space="preserve">7800</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t xml:space="preserve">8184584</t>
+          <t xml:space="preserve">382557, 382558, 382559</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H106">
-        <v>532</v>
+        <v>1019</v>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t xml:space="preserve">200045484</t>
+          <t xml:space="preserve">311074127</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-02-10</t>
+          <t xml:space="preserve">2024-09-18</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
@@ -6391,35 +6391,35 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bredgade 51B</t>
+          <t xml:space="preserve">Ålbækvej 18</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t xml:space="preserve">7870</t>
+          <t xml:space="preserve">7860</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t xml:space="preserve">8184584</t>
+          <t xml:space="preserve">4074902</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H107">
-        <v>445</v>
+        <v>872</v>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t xml:space="preserve">200045485</t>
+          <t xml:space="preserve">311156172</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-02-10</t>
+          <t xml:space="preserve">2026-01-29</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
@@ -6451,17 +6451,17 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ginnerupvej 4</t>
+          <t xml:space="preserve">Kærvej 7</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t xml:space="preserve">7860</t>
+          <t xml:space="preserve">7870</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t xml:space="preserve">8798318</t>
+          <t xml:space="preserve">8724731</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -6470,16 +6470,16 @@
         </is>
       </c>
       <c r="H108">
-        <v>403</v>
+        <v>358</v>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t xml:space="preserve">310017203</t>
+          <t xml:space="preserve">311197742</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t xml:space="preserve">2022-12-12</t>
+          <t xml:space="preserve">2026-08-31</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
@@ -6511,45 +6511,45 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brårupvej 126</t>
+          <t xml:space="preserve">Østerrisvej 36B</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t xml:space="preserve">7800</t>
+          <t xml:space="preserve">7840</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t xml:space="preserve">5580269</t>
+          <t xml:space="preserve">4050024</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H109">
-        <v>272</v>
+        <v>531</v>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t xml:space="preserve">311071797</t>
+          <t xml:space="preserve">311198907</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t xml:space="preserve">2024-09-04</t>
+          <t xml:space="preserve">2026-09-06</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -6571,45 +6571,45 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ålbækvej 18</t>
+          <t xml:space="preserve">Hejlskovvej 25</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t xml:space="preserve">7860</t>
+          <t xml:space="preserve">7840</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t xml:space="preserve">4074902</t>
+          <t xml:space="preserve">4055746</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H110">
-        <v>872</v>
+        <v>259</v>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t xml:space="preserve">311156172</t>
+          <t xml:space="preserve">311199649</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-29</t>
+          <t xml:space="preserve">2026-09-09</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -6631,45 +6631,45 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kærvej 7</t>
+          <t xml:space="preserve">Rosenbakken 4</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t xml:space="preserve">7870</t>
+          <t xml:space="preserve">7800</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t xml:space="preserve">8724731</t>
+          <t xml:space="preserve">8899384</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H111">
-        <v>358</v>
+        <v>882</v>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t xml:space="preserve">311197742</t>
+          <t xml:space="preserve">311199648</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-31</t>
+          <t xml:space="preserve">2026-09-09</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -6691,7 +6691,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østerrisvej 36B</t>
+          <t xml:space="preserve">Skolevej 13</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -6701,25 +6701,25 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t xml:space="preserve">4050024</t>
+          <t xml:space="preserve">4050055</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H112">
-        <v>531</v>
+        <v>6478</v>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t xml:space="preserve">311198907</t>
+          <t xml:space="preserve">311199661</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-06</t>
+          <t xml:space="preserve">2026-09-09</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
@@ -6751,17 +6751,17 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 13</t>
+          <t xml:space="preserve">Fasanvej 7</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t xml:space="preserve">7840</t>
+          <t xml:space="preserve">7870</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t xml:space="preserve">4050055</t>
+          <t xml:space="preserve">4059105</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -6770,16 +6770,16 @@
         </is>
       </c>
       <c r="H113">
-        <v>6478</v>
+        <v>292</v>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t xml:space="preserve">311199661</t>
+          <t xml:space="preserve">311201294</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-09</t>
+          <t xml:space="preserve">2026-09-19</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
@@ -6811,35 +6811,35 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hejlskovvej 25</t>
+          <t xml:space="preserve">Præstelund 5</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t xml:space="preserve">7840</t>
+          <t xml:space="preserve">7870</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t xml:space="preserve">4055746</t>
+          <t xml:space="preserve">7806050</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H114">
-        <v>259</v>
+        <v>309</v>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t xml:space="preserve">311199649</t>
+          <t xml:space="preserve">311201293</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-09</t>
+          <t xml:space="preserve">2026-09-19</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
@@ -6871,7 +6871,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rosenbakken 4</t>
+          <t xml:space="preserve">Norgaardsvej 21</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -6881,25 +6881,25 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t xml:space="preserve">8899384</t>
+          <t xml:space="preserve">5577994</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H115">
-        <v>882</v>
+        <v>1009</v>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t xml:space="preserve">311199648</t>
+          <t xml:space="preserve">311204539</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-09</t>
+          <t xml:space="preserve">2026-10-05</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
@@ -6931,17 +6931,17 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fasanvej 7</t>
+          <t xml:space="preserve">Dalgas Alle 22</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t xml:space="preserve">7870</t>
+          <t xml:space="preserve">7800</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t xml:space="preserve">4059105</t>
+          <t xml:space="preserve">5581102</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -6950,16 +6950,16 @@
         </is>
       </c>
       <c r="H116">
-        <v>292</v>
+        <v>9399</v>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t xml:space="preserve">311201294</t>
+          <t xml:space="preserve">311207277</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-19</t>
+          <t xml:space="preserve">2026-10-18</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
@@ -6991,35 +6991,35 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Præstelund 5</t>
+          <t xml:space="preserve">Frederiksgade 21L</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t xml:space="preserve">7870</t>
+          <t xml:space="preserve">7800</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t xml:space="preserve">7806050</t>
+          <t xml:space="preserve">5575936</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H117">
-        <v>309</v>
+        <v>1791</v>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t xml:space="preserve">311201293</t>
+          <t xml:space="preserve">311213851</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-19</t>
+          <t xml:space="preserve">2026-11-23</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
@@ -7051,17 +7051,17 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Norgaardsvej 21</t>
+          <t xml:space="preserve">Hejlskovvej 24</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t xml:space="preserve">7800</t>
+          <t xml:space="preserve">7840</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t xml:space="preserve">5577994</t>
+          <t xml:space="preserve">4055731</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -7070,16 +7070,16 @@
         </is>
       </c>
       <c r="H118">
-        <v>1009</v>
+        <v>1902</v>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t xml:space="preserve">311204539</t>
+          <t xml:space="preserve">311215076</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-05</t>
+          <t xml:space="preserve">2026-11-30</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
@@ -7111,17 +7111,17 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dalgas Alle 22</t>
+          <t xml:space="preserve">Stoholmvej 9</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t xml:space="preserve">7800</t>
+          <t xml:space="preserve">7840</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t xml:space="preserve">5581102</t>
+          <t xml:space="preserve">4050673</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -7130,16 +7130,16 @@
         </is>
       </c>
       <c r="H119">
-        <v>9399</v>
+        <v>580</v>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t xml:space="preserve">311207277</t>
+          <t xml:space="preserve">311215058</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-18</t>
+          <t xml:space="preserve">2026-11-30</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
@@ -7171,7 +7171,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frederiksgade 21L</t>
+          <t xml:space="preserve">Brårupvej 94</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -7181,25 +7181,25 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t xml:space="preserve">5575936</t>
+          <t xml:space="preserve">5582112</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H120">
-        <v>1791</v>
+        <v>962</v>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t xml:space="preserve">311213851</t>
+          <t xml:space="preserve">311215617</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-23</t>
+          <t xml:space="preserve">2026-12-02</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
@@ -7231,35 +7231,35 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stoholmvej 9</t>
+          <t xml:space="preserve">Skovbakken 2</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t xml:space="preserve">7840</t>
+          <t xml:space="preserve">7870</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t xml:space="preserve">4050673</t>
+          <t xml:space="preserve">4068043</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H121">
-        <v>580</v>
+        <v>269</v>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t xml:space="preserve">311215058</t>
+          <t xml:space="preserve">311216686</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-30</t>
+          <t xml:space="preserve">2026-12-08</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
@@ -7291,35 +7291,35 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hejlskovvej 24</t>
+          <t xml:space="preserve">Skovbakken 4</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t xml:space="preserve">7840</t>
+          <t xml:space="preserve">7870</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t xml:space="preserve">4055731</t>
+          <t xml:space="preserve">4068043</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H122">
-        <v>1902</v>
+        <v>1342</v>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t xml:space="preserve">311215076</t>
+          <t xml:space="preserve">311216682</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-30</t>
+          <t xml:space="preserve">2026-12-08</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
@@ -7351,7 +7351,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brårupvej 94</t>
+          <t xml:space="preserve">Skovbakken 4</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -7361,25 +7361,25 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t xml:space="preserve">5582112</t>
+          <t xml:space="preserve">4068043</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H123">
-        <v>962</v>
+        <v>2601</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t xml:space="preserve">311215617</t>
+          <t xml:space="preserve">311216682</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-02</t>
+          <t xml:space="preserve">2026-12-08</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
@@ -7426,11 +7426,11 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H124">
-        <v>1342</v>
+        <v>658</v>
       </c>
       <c r="I124" t="inlineStr">
         <is>
@@ -7471,35 +7471,35 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovbakken 4</t>
+          <t xml:space="preserve">Hejlskovvej 27</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t xml:space="preserve">7800</t>
+          <t xml:space="preserve">7840</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t xml:space="preserve">4068043</t>
+          <t xml:space="preserve">4055746</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H125">
-        <v>2601</v>
+        <v>1776</v>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t xml:space="preserve">311216682</t>
+          <t xml:space="preserve">311223000</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-08</t>
+          <t xml:space="preserve">2027-01-17</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
@@ -7531,35 +7531,35 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovbakken 4</t>
+          <t xml:space="preserve">Rudemøllevej 3</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t xml:space="preserve">7870</t>
+          <t xml:space="preserve">7800</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t xml:space="preserve">4068043</t>
+          <t xml:space="preserve">4057006</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H126">
-        <v>658</v>
+        <v>1336</v>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t xml:space="preserve">311216682</t>
+          <t xml:space="preserve">311224661</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-08</t>
+          <t xml:space="preserve">2027-01-26</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
@@ -7591,35 +7591,35 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovbakken 2</t>
+          <t xml:space="preserve">Rudemøllevej 3A</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t xml:space="preserve">7870</t>
+          <t xml:space="preserve">7800</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t xml:space="preserve">4068043</t>
+          <t xml:space="preserve">4057006</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H127">
-        <v>269</v>
+        <v>1455</v>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t xml:space="preserve">311216686</t>
+          <t xml:space="preserve">311224665</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-08</t>
+          <t xml:space="preserve">2027-01-26</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
@@ -7651,17 +7651,17 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hejlskovvej 27</t>
+          <t xml:space="preserve">Vejbyvej 5</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t xml:space="preserve">7840</t>
+          <t xml:space="preserve">7860</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t xml:space="preserve">4055746</t>
+          <t xml:space="preserve">100007822</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
@@ -7670,16 +7670,16 @@
         </is>
       </c>
       <c r="H128">
-        <v>1776</v>
+        <v>2115</v>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t xml:space="preserve">311223000</t>
+          <t xml:space="preserve">311248999</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-01-17</t>
+          <t xml:space="preserve">2027-05-22</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
@@ -7711,7 +7711,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rudemøllevej 3</t>
+          <t xml:space="preserve">Hjaltesvej 7A</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -7721,25 +7721,25 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t xml:space="preserve">4057006</t>
+          <t xml:space="preserve">380712</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H129">
-        <v>1336</v>
+        <v>414</v>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t xml:space="preserve">311224661</t>
+          <t xml:space="preserve">311259954</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-01-26</t>
+          <t xml:space="preserve">2027-07-10</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
@@ -7771,7 +7771,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rudemøllevej 3A</t>
+          <t xml:space="preserve">Egerisvej 12</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -7781,25 +7781,25 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t xml:space="preserve">4057006</t>
+          <t xml:space="preserve">381206, 381207</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H130">
-        <v>1455</v>
+        <v>1717</v>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t xml:space="preserve">311224665</t>
+          <t xml:space="preserve">311260356</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-01-26</t>
+          <t xml:space="preserve">2027-07-12</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
@@ -7831,35 +7831,35 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vejbyvej 5</t>
+          <t xml:space="preserve">Idrætsvej 2</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t xml:space="preserve">7860</t>
+          <t xml:space="preserve">7870</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t xml:space="preserve">100007822</t>
+          <t xml:space="preserve">4065067</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H131">
-        <v>2115</v>
+        <v>1898</v>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t xml:space="preserve">311248999</t>
+          <t xml:space="preserve">311269956</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-05-22</t>
+          <t xml:space="preserve">2027-08-31</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
@@ -7906,11 +7906,11 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H132">
-        <v>1898</v>
+        <v>1477</v>
       </c>
       <c r="I132" t="inlineStr">
         <is>
@@ -7951,35 +7951,35 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t xml:space="preserve">Idrætsvej 2</t>
+          <t xml:space="preserve">Stoholmvej 24</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t xml:space="preserve">7870</t>
+          <t xml:space="preserve">7840</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t xml:space="preserve">4065067</t>
+          <t xml:space="preserve">8116502</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H133">
-        <v>1477</v>
+        <v>1500</v>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t xml:space="preserve">311269956</t>
+          <t xml:space="preserve">311272174</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-08-31</t>
+          <t xml:space="preserve">2027-09-11</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
@@ -8011,17 +8011,17 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stoholmvej 24</t>
+          <t xml:space="preserve">H C Ørsteds Vej 4</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t xml:space="preserve">7840</t>
+          <t xml:space="preserve">7800</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t xml:space="preserve">8116502</t>
+          <t xml:space="preserve">7893354</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
@@ -8030,16 +8030,16 @@
         </is>
       </c>
       <c r="H134">
-        <v>1500</v>
+        <v>1091</v>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t xml:space="preserve">311272174</t>
+          <t xml:space="preserve">311274198</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-09-11</t>
+          <t xml:space="preserve">2027-09-21</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
@@ -8071,7 +8071,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t xml:space="preserve">H C Ørsteds Vej 4</t>
+          <t xml:space="preserve">Bjarkesvej 2</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -8081,7 +8081,7 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t xml:space="preserve">7893354</t>
+          <t xml:space="preserve">5582684</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
@@ -8090,16 +8090,16 @@
         </is>
       </c>
       <c r="H135">
-        <v>1091</v>
+        <v>701</v>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t xml:space="preserve">311274198</t>
+          <t xml:space="preserve">311274934</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-09-21</t>
+          <t xml:space="preserve">2027-09-25</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
@@ -8191,7 +8191,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bjarkesvej 2</t>
+          <t xml:space="preserve">Jeppe Aakjærsvej 18</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -8201,7 +8201,7 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t xml:space="preserve">5582684</t>
+          <t xml:space="preserve">9441948</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
@@ -8210,16 +8210,16 @@
         </is>
       </c>
       <c r="H137">
-        <v>701</v>
+        <v>445</v>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t xml:space="preserve">311274934</t>
+          <t xml:space="preserve">311280025</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-09-25</t>
+          <t xml:space="preserve">2027-10-23</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
@@ -8251,7 +8251,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jeppe Aakjærsvej 18</t>
+          <t xml:space="preserve">Rosenbakken 2</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -8261,25 +8261,25 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t xml:space="preserve">9441948</t>
+          <t xml:space="preserve">8899384</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="H138">
-        <v>445</v>
+        <v>260</v>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t xml:space="preserve">311280025</t>
+          <t xml:space="preserve">311283218</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-10-23</t>
+          <t xml:space="preserve">2027-11-10</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
@@ -8371,7 +8371,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rosenbakken 2</t>
+          <t xml:space="preserve">Rosenbakken 8</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -8386,20 +8386,20 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H140">
-        <v>260</v>
+        <v>5926</v>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t xml:space="preserve">311283218</t>
+          <t xml:space="preserve">311283462</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-11-10</t>
+          <t xml:space="preserve">2027-11-13</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
@@ -8431,7 +8431,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rosenbakken 8</t>
+          <t xml:space="preserve">Asylgade 4</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -8441,25 +8441,25 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t xml:space="preserve">8899384</t>
+          <t xml:space="preserve">5575145</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H141">
-        <v>5926</v>
+        <v>337</v>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t xml:space="preserve">311283462</t>
+          <t xml:space="preserve">311284088</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-11-13</t>
+          <t xml:space="preserve">2027-11-16</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
@@ -8491,7 +8491,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t xml:space="preserve">Asylgade 4</t>
+          <t xml:space="preserve">Smøgen 2B</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -8501,7 +8501,7 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t xml:space="preserve">5575145</t>
+          <t xml:space="preserve">5575376</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
@@ -8510,16 +8510,16 @@
         </is>
       </c>
       <c r="H142">
-        <v>337</v>
+        <v>590</v>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t xml:space="preserve">311284088</t>
+          <t xml:space="preserve">311285478</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-11-16</t>
+          <t xml:space="preserve">2027-11-23</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
@@ -8551,7 +8551,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t xml:space="preserve">Smøgen 2B</t>
+          <t xml:space="preserve">Furvej 7</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -8561,25 +8561,25 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t xml:space="preserve">5575376</t>
+          <t xml:space="preserve">8899482</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">30</t>
         </is>
       </c>
       <c r="H143">
-        <v>590</v>
+        <v>1903</v>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t xml:space="preserve">311285478</t>
+          <t xml:space="preserve">311288301</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-11-23</t>
+          <t xml:space="preserve">2027-12-12</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
@@ -8611,7 +8611,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kisumvej 28A</t>
+          <t xml:space="preserve">Furvej 7</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -8621,20 +8621,20 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t xml:space="preserve">4508315</t>
+          <t xml:space="preserve">8899482</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H144">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t xml:space="preserve">311288314</t>
+          <t xml:space="preserve">311288301</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
@@ -8671,7 +8671,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Furvej 9</t>
+          <t xml:space="preserve">Furvej 7B</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -8686,11 +8686,11 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">31</t>
         </is>
       </c>
       <c r="H145">
-        <v>6222</v>
+        <v>410</v>
       </c>
       <c r="I145" t="inlineStr">
         <is>
@@ -8731,7 +8731,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t xml:space="preserve">Furvej 9B</t>
+          <t xml:space="preserve">Furvej 9</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -8746,15 +8746,15 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H146">
-        <v>739</v>
+        <v>6222</v>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t xml:space="preserve">311288301</t>
+          <t xml:space="preserve">311288292</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
@@ -8791,7 +8791,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t xml:space="preserve">Furvej 9D</t>
+          <t xml:space="preserve">Furvej 9B</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -8806,15 +8806,15 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H147">
-        <v>252</v>
+        <v>739</v>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t xml:space="preserve">311288301</t>
+          <t xml:space="preserve">311288299</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
@@ -8851,7 +8851,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t xml:space="preserve">Furvej 7</t>
+          <t xml:space="preserve">Furvej 9B</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -8866,11 +8866,11 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t xml:space="preserve">30</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="H148">
-        <v>1903</v>
+        <v>1260</v>
       </c>
       <c r="I148" t="inlineStr">
         <is>
@@ -8911,7 +8911,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t xml:space="preserve">Furvej 7B</t>
+          <t xml:space="preserve">Furvej 9D</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -8926,11 +8926,11 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t xml:space="preserve">31</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H149">
-        <v>410</v>
+        <v>252</v>
       </c>
       <c r="I149" t="inlineStr">
         <is>
@@ -8971,7 +8971,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t xml:space="preserve">Furvej 7</t>
+          <t xml:space="preserve">Kisumvej 28A</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -8981,20 +8981,20 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t xml:space="preserve">8899482</t>
+          <t xml:space="preserve">4508315</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H150">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t xml:space="preserve">311288301</t>
+          <t xml:space="preserve">311288314</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
@@ -9031,7 +9031,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t xml:space="preserve">Furvej 9B</t>
+          <t xml:space="preserve">Furvej 9A</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -9046,20 +9046,20 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="H151">
-        <v>1260</v>
+        <v>1969</v>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t xml:space="preserve">311288301</t>
+          <t xml:space="preserve">311288786</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-12</t>
+          <t xml:space="preserve">2027-12-14</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
@@ -9091,7 +9091,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t xml:space="preserve">Furvej 9A</t>
+          <t xml:space="preserve">Furvej 9E</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -9106,20 +9106,20 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H152">
-        <v>1969</v>
+        <v>804</v>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t xml:space="preserve">311288786</t>
+          <t xml:space="preserve">311289322</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-14</t>
+          <t xml:space="preserve">2027-12-18</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
@@ -9151,7 +9151,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t xml:space="preserve">Furvej 9E</t>
+          <t xml:space="preserve">Frederiksgade 21K</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -9161,25 +9161,25 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t xml:space="preserve">8899482</t>
+          <t xml:space="preserve">5575936</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H153">
-        <v>804</v>
+        <v>4596</v>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t xml:space="preserve">311289322</t>
+          <t xml:space="preserve">311289957</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-18</t>
+          <t xml:space="preserve">2027-12-21</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
@@ -9211,7 +9211,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frederiksgade 21K</t>
+          <t xml:space="preserve">Arvikavej 1</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -9221,25 +9221,25 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t xml:space="preserve">5575936</t>
+          <t xml:space="preserve">5581148</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="H154">
-        <v>4596</v>
+        <v>360</v>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t xml:space="preserve">311289957</t>
+          <t xml:space="preserve">311346281</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-21</t>
+          <t xml:space="preserve">2028-11-12</t>
         </is>
       </c>
       <c r="K154" t="inlineStr">
@@ -9271,7 +9271,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t xml:space="preserve">Arvikavej 1</t>
+          <t xml:space="preserve">Brårupvej 92</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -9281,25 +9281,25 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t xml:space="preserve">5581148</t>
+          <t xml:space="preserve">5580471</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H155">
-        <v>360</v>
+        <v>674</v>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t xml:space="preserve">311346319</t>
+          <t xml:space="preserve">311347531</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-11-12</t>
+          <t xml:space="preserve">2028-11-19</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
@@ -9391,7 +9391,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brårupvej 92</t>
+          <t xml:space="preserve">Brårupgade 18A</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -9401,7 +9401,7 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t xml:space="preserve">5580471</t>
+          <t xml:space="preserve">100011734</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
@@ -9410,16 +9410,16 @@
         </is>
       </c>
       <c r="H157">
-        <v>674</v>
+        <v>403</v>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t xml:space="preserve">311347531</t>
+          <t xml:space="preserve">311458075</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-11-19</t>
+          <t xml:space="preserve">2030-09-01</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
@@ -9451,7 +9451,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brårupgade 18A</t>
+          <t xml:space="preserve">Brårupgade 18C</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -9466,20 +9466,20 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H158">
-        <v>403</v>
+        <v>1116</v>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t xml:space="preserve">311458075</t>
+          <t xml:space="preserve">311458304</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-09-01</t>
+          <t xml:space="preserve">2030-09-02</t>
         </is>
       </c>
       <c r="K158" t="inlineStr">
@@ -9511,7 +9511,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brårupgade 18C</t>
+          <t xml:space="preserve">Engvej 19</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -9521,25 +9521,25 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t xml:space="preserve">100011734</t>
+          <t xml:space="preserve">8899386</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H159">
-        <v>1116</v>
+        <v>607</v>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t xml:space="preserve">311458304</t>
+          <t xml:space="preserve">311464353</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-09-02</t>
+          <t xml:space="preserve">2030-09-30</t>
         </is>
       </c>
       <c r="K159" t="inlineStr">
@@ -9586,11 +9586,11 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H160">
-        <v>607</v>
+        <v>378</v>
       </c>
       <c r="I160" t="inlineStr">
         <is>
@@ -9646,7 +9646,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H161">
@@ -9691,7 +9691,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t xml:space="preserve">Engvej 19</t>
+          <t xml:space="preserve">Skyttevej 6</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -9701,25 +9701,25 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t xml:space="preserve">8899386</t>
+          <t xml:space="preserve">5580961</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H162">
-        <v>378</v>
+        <v>1408</v>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t xml:space="preserve">311464353</t>
+          <t xml:space="preserve">311468503</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-09-30</t>
+          <t xml:space="preserve">2030-10-21</t>
         </is>
       </c>
       <c r="K162" t="inlineStr">
@@ -9751,35 +9751,35 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skyttevej 6</t>
+          <t xml:space="preserve">Nørre Ramsingvej 21A</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t xml:space="preserve">7800</t>
+          <t xml:space="preserve">7860</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t xml:space="preserve">5580961</t>
+          <t xml:space="preserve">4075942</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H163">
-        <v>1408</v>
+        <v>855</v>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t xml:space="preserve">311468503</t>
+          <t xml:space="preserve">311483171</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-10-21</t>
+          <t xml:space="preserve">2030-12-16</t>
         </is>
       </c>
       <c r="K163" t="inlineStr">
@@ -9811,7 +9811,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørre Ramsingvej 21A</t>
+          <t xml:space="preserve">Nørre Ramsingvej 21B</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -9826,15 +9826,15 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H164">
-        <v>855</v>
+        <v>324</v>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t xml:space="preserve">311483171</t>
+          <t xml:space="preserve">311483170</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
@@ -9871,35 +9871,35 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørre Ramsingvej 21B</t>
+          <t xml:space="preserve">Violvej 2A</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t xml:space="preserve">7860</t>
+          <t xml:space="preserve">7800</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t xml:space="preserve">4075942</t>
+          <t xml:space="preserve">10108979</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H165">
-        <v>324</v>
+        <v>1651</v>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t xml:space="preserve">311483170</t>
+          <t xml:space="preserve">311495820</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-16</t>
+          <t xml:space="preserve">2031-02-16</t>
         </is>
       </c>
       <c r="K165" t="inlineStr">
@@ -9931,7 +9931,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t xml:space="preserve">Violvej 2A</t>
+          <t xml:space="preserve">Bjarkesvej 4</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -9941,7 +9941,7 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t xml:space="preserve">10108979</t>
+          <t xml:space="preserve">5582681</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
@@ -9950,16 +9950,16 @@
         </is>
       </c>
       <c r="H166">
-        <v>1651</v>
+        <v>1436</v>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t xml:space="preserve">311495820</t>
+          <t xml:space="preserve">311497320</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-02-16</t>
+          <t xml:space="preserve">2031-02-22</t>
         </is>
       </c>
       <c r="K166" t="inlineStr">
@@ -9991,7 +9991,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bjarkesvej 4</t>
+          <t xml:space="preserve">H C Ørsteds Vej 1</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -10001,7 +10001,7 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t xml:space="preserve">5582681</t>
+          <t xml:space="preserve">5581565</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
@@ -10010,16 +10010,16 @@
         </is>
       </c>
       <c r="H167">
-        <v>1436</v>
+        <v>1178</v>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t xml:space="preserve">311497320</t>
+          <t xml:space="preserve">311498972</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-02-22</t>
+          <t xml:space="preserve">2031-02-26</t>
         </is>
       </c>
       <c r="K167" t="inlineStr">
@@ -10051,17 +10051,17 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t xml:space="preserve">H C Ørsteds Vej 1</t>
+          <t xml:space="preserve">Skolebakken 8</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t xml:space="preserve">7800</t>
+          <t xml:space="preserve">7870</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t xml:space="preserve">5581565</t>
+          <t xml:space="preserve">4062718</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
@@ -10070,16 +10070,16 @@
         </is>
       </c>
       <c r="H168">
-        <v>1178</v>
+        <v>3914</v>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t xml:space="preserve">311498972</t>
+          <t xml:space="preserve">311503309</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-02-26</t>
+          <t xml:space="preserve">2031-03-15</t>
         </is>
       </c>
       <c r="K168" t="inlineStr">
@@ -10111,7 +10111,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolebakken 8</t>
+          <t xml:space="preserve">Hovedgaden 40</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -10121,25 +10121,25 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t xml:space="preserve">4062718</t>
+          <t xml:space="preserve">1803393</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H169">
-        <v>3914</v>
+        <v>360</v>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t xml:space="preserve">311503309</t>
+          <t xml:space="preserve">311505041</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-03-15</t>
+          <t xml:space="preserve">2031-03-19</t>
         </is>
       </c>
       <c r="K169" t="inlineStr">
@@ -10171,17 +10171,17 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovedgaden 40</t>
+          <t xml:space="preserve">Stoholmvej 26</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t xml:space="preserve">7870</t>
+          <t xml:space="preserve">7840</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t xml:space="preserve">1803393</t>
+          <t xml:space="preserve">8116502</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
@@ -10190,16 +10190,16 @@
         </is>
       </c>
       <c r="H170">
-        <v>360</v>
+        <v>403</v>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t xml:space="preserve">311505041</t>
+          <t xml:space="preserve">311506012</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-03-19</t>
+          <t xml:space="preserve">2031-03-23</t>
         </is>
       </c>
       <c r="K170" t="inlineStr">
@@ -10231,35 +10231,35 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stoholmvej 26</t>
+          <t xml:space="preserve">H C Ørsteds Vej 4</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t xml:space="preserve">7840</t>
+          <t xml:space="preserve">7800</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t xml:space="preserve">8116502</t>
+          <t xml:space="preserve">7893354</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H171">
-        <v>403</v>
+        <v>380</v>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t xml:space="preserve">311506012</t>
+          <t xml:space="preserve">311510560</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-03-23</t>
+          <t xml:space="preserve">2031-04-07</t>
         </is>
       </c>
       <c r="K171" t="inlineStr">
@@ -10291,7 +10291,7 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t xml:space="preserve">H C Ørsteds Vej 4</t>
+          <t xml:space="preserve">H C Ørsteds Vej 6B</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -10306,15 +10306,15 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H172">
-        <v>380</v>
+        <v>970</v>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t xml:space="preserve">311510560</t>
+          <t xml:space="preserve">311510570</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
@@ -10351,35 +10351,35 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t xml:space="preserve">H C Ørsteds Vej 6B</t>
+          <t xml:space="preserve">Grønnegade 5</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t xml:space="preserve">7800</t>
+          <t xml:space="preserve">7870</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t xml:space="preserve">7893354</t>
+          <t xml:space="preserve">9119581</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H173">
-        <v>970</v>
+        <v>1178</v>
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t xml:space="preserve">311510570</t>
+          <t xml:space="preserve">311542226</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-04-07</t>
+          <t xml:space="preserve">2031-08-20</t>
         </is>
       </c>
       <c r="K173" t="inlineStr">
@@ -10411,7 +10411,7 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grønnegade 5</t>
+          <t xml:space="preserve">Grønnegade 5A</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
@@ -10426,11 +10426,11 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H174">
-        <v>1178</v>
+        <v>1483</v>
       </c>
       <c r="I174" t="inlineStr">
         <is>
@@ -10591,7 +10591,7 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grønnegade 5A</t>
+          <t xml:space="preserve">Sallingsundvej 26</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
@@ -10606,11 +10606,11 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H177">
-        <v>1483</v>
+        <v>388</v>
       </c>
       <c r="I177" t="inlineStr">
         <is>
@@ -10651,35 +10651,35 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sallingsundvej 26</t>
+          <t xml:space="preserve">Rådhuspladsen 2</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t xml:space="preserve">7870</t>
+          <t xml:space="preserve">7800</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t xml:space="preserve">9119581</t>
+          <t xml:space="preserve">5575466</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H178">
-        <v>388</v>
+        <v>4897</v>
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t xml:space="preserve">311542226</t>
+          <t xml:space="preserve">311564028</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-20</t>
+          <t xml:space="preserve">2031-11-24</t>
         </is>
       </c>
       <c r="K178" t="inlineStr">
@@ -10711,7 +10711,7 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rådhuspladsen 2</t>
+          <t xml:space="preserve">Odgaardsvej 15B</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
@@ -10721,25 +10721,25 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t xml:space="preserve">5575466</t>
+          <t xml:space="preserve">9524001</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H179">
-        <v>4897</v>
+        <v>875</v>
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t xml:space="preserve">311564028</t>
+          <t xml:space="preserve">311571055</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-11-24</t>
+          <t xml:space="preserve">2032-01-06</t>
         </is>
       </c>
       <c r="K179" t="inlineStr">
@@ -10771,7 +10771,7 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t xml:space="preserve">Odgaardsvej 15B</t>
+          <t xml:space="preserve">Torvegade 10</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
@@ -10781,25 +10781,25 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t xml:space="preserve">9524001</t>
+          <t xml:space="preserve">5575466</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H180">
-        <v>875</v>
+        <v>2584</v>
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t xml:space="preserve">311571055</t>
+          <t xml:space="preserve">311573049</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-01-06</t>
+          <t xml:space="preserve">2032-01-18</t>
         </is>
       </c>
       <c r="K180" t="inlineStr">
@@ -10891,7 +10891,7 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t xml:space="preserve">Torvegade 10</t>
+          <t xml:space="preserve">Kisumvej 28C</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
@@ -10901,25 +10901,25 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t xml:space="preserve">5575466</t>
+          <t xml:space="preserve">4508315</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H182">
-        <v>2584</v>
+        <v>1532</v>
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t xml:space="preserve">311573049</t>
+          <t xml:space="preserve">311575593</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-01-18</t>
+          <t xml:space="preserve">2032-01-31</t>
         </is>
       </c>
       <c r="K182" t="inlineStr">
@@ -10951,7 +10951,7 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kisumvej 28C</t>
+          <t xml:space="preserve">Kisumvej 30</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -10966,20 +10966,20 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H183">
-        <v>1532</v>
+        <v>1230</v>
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t xml:space="preserve">311575593</t>
+          <t xml:space="preserve">311575922</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-01-31</t>
+          <t xml:space="preserve">2032-02-01</t>
         </is>
       </c>
       <c r="K183" t="inlineStr">
@@ -11011,17 +11011,17 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kisumvej 30</t>
+          <t xml:space="preserve">Kløvermarken 4</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t xml:space="preserve">7800</t>
+          <t xml:space="preserve">7860</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t xml:space="preserve">4508315</t>
+          <t xml:space="preserve">8747981</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
@@ -11030,16 +11030,16 @@
         </is>
       </c>
       <c r="H184">
-        <v>1230</v>
+        <v>369</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t xml:space="preserve">311575922</t>
+          <t xml:space="preserve">311578920</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-02-01</t>
+          <t xml:space="preserve">2032-02-15</t>
         </is>
       </c>
       <c r="K184" t="inlineStr">
@@ -11071,35 +11071,35 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kløvermarken 4</t>
+          <t xml:space="preserve">Bilstrupvej 27A</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t xml:space="preserve">7860</t>
+          <t xml:space="preserve">7800</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t xml:space="preserve">8747981</t>
+          <t xml:space="preserve">5581674</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H185">
-        <v>369</v>
+        <v>536</v>
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t xml:space="preserve">311578920</t>
+          <t xml:space="preserve">311585347</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-02-15</t>
+          <t xml:space="preserve">2032-03-15</t>
         </is>
       </c>
       <c r="K185" t="inlineStr">
@@ -11131,7 +11131,7 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jægervej 16</t>
+          <t xml:space="preserve">Bilstrupvej 27B</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
@@ -11146,11 +11146,11 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H186">
-        <v>709</v>
+        <v>616</v>
       </c>
       <c r="I186" t="inlineStr">
         <is>
@@ -11191,7 +11191,7 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jægervej 16A</t>
+          <t xml:space="preserve">Bilstrupvej 27C</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
@@ -11206,15 +11206,15 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H187">
-        <v>284</v>
+        <v>630</v>
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t xml:space="preserve">311585347</t>
+          <t xml:space="preserve">311585357</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
@@ -11251,7 +11251,7 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bilstrupvej 27A</t>
+          <t xml:space="preserve">Bilstrupvej 27D</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
@@ -11266,15 +11266,15 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H188">
-        <v>536</v>
+        <v>625</v>
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t xml:space="preserve">311585347</t>
+          <t xml:space="preserve">311585356</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
@@ -11311,7 +11311,7 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bilstrupvej 27B</t>
+          <t xml:space="preserve">Bilstrupvej 27E</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
@@ -11326,11 +11326,11 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="H189">
-        <v>616</v>
+        <v>260</v>
       </c>
       <c r="I189" t="inlineStr">
         <is>
@@ -11371,7 +11371,7 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bilstrupvej 27C</t>
+          <t xml:space="preserve">Jægervej 16</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
@@ -11386,15 +11386,15 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="H190">
-        <v>630</v>
+        <v>709</v>
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t xml:space="preserve">311585347</t>
+          <t xml:space="preserve">311585352</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
@@ -11431,7 +11431,7 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bilstrupvej 27D</t>
+          <t xml:space="preserve">Jægervej 16A</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
@@ -11446,11 +11446,11 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="H191">
-        <v>625</v>
+        <v>284</v>
       </c>
       <c r="I191" t="inlineStr">
         <is>
@@ -11491,7 +11491,7 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bilstrupvej 27E</t>
+          <t xml:space="preserve">Præstevejen 28</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
@@ -11501,25 +11501,25 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t xml:space="preserve">5581674</t>
+          <t xml:space="preserve">381665, 381666</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H192">
-        <v>260</v>
+        <v>844</v>
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t xml:space="preserve">311585347</t>
+          <t xml:space="preserve">311594036</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-15</t>
+          <t xml:space="preserve">2032-04-21</t>
         </is>
       </c>
       <c r="K192" t="inlineStr">
@@ -11971,7 +11971,7 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestergårdsvej 8A</t>
+          <t xml:space="preserve">Vestergårdsvej 8</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
@@ -11981,20 +11981,20 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t xml:space="preserve">4059864</t>
+          <t xml:space="preserve">4060626</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H200">
-        <v>376</v>
+        <v>2640</v>
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t xml:space="preserve">311761932</t>
+          <t xml:space="preserve">311761873</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
@@ -12031,7 +12031,7 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestergårdsvej 8</t>
+          <t xml:space="preserve">Vestergårdsvej 8A</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
@@ -12041,20 +12041,20 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t xml:space="preserve">4060626</t>
+          <t xml:space="preserve">4059864</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H201">
-        <v>2640</v>
+        <v>376</v>
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t xml:space="preserve">311761873</t>
+          <t xml:space="preserve">311761932</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">

--- a/public/exports/29189579.xlsx
+++ b/public/exports/29189579.xlsx
@@ -5454,7 +5454,7 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t xml:space="preserve">200027486</t>
+          <t xml:space="preserve">200027494</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -5574,7 +5574,7 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t xml:space="preserve">200027518</t>
+          <t xml:space="preserve">200027494</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -9234,7 +9234,7 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t xml:space="preserve">311346281</t>
+          <t xml:space="preserve">311346319</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
@@ -11274,7 +11274,7 @@
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t xml:space="preserve">311585356</t>
+          <t xml:space="preserve">311585347</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">

--- a/public/exports/29189579.xlsx
+++ b/public/exports/29189579.xlsx
@@ -9,7 +9,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L219"/>
+  <dimension ref="A1:M219"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -59,15 +59,20 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energimærkningsfirma</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
           <t xml:space="preserve">Gyldig til</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t xml:space="preserve">Status</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler gyldigt mærke</t>
         </is>
@@ -124,10 +129,15 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -184,10 +194,15 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -244,10 +259,15 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -304,10 +324,15 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -364,10 +389,15 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -424,10 +454,15 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -484,10 +519,15 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -544,10 +584,15 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -604,10 +649,15 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -664,10 +714,15 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -724,10 +779,15 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -784,10 +844,15 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -844,10 +909,15 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -904,10 +974,15 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -964,10 +1039,15 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1024,10 +1104,15 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1084,10 +1169,15 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1144,10 +1234,15 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1204,10 +1299,15 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1264,10 +1364,15 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1324,10 +1429,15 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1384,10 +1494,15 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
+      <c r="M23" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1444,10 +1559,15 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
+      <c r="M24" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1504,10 +1624,15 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1564,10 +1689,15 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="M26" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1624,10 +1754,15 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
+      <c r="M27" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1684,10 +1819,15 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
+      <c r="M28" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1744,10 +1884,15 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
+      <c r="M29" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1804,10 +1949,15 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
+      <c r="M30" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1864,10 +2014,15 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr">
+      <c r="M31" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1924,10 +2079,15 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr">
+      <c r="M32" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1984,10 +2144,15 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr">
+      <c r="M33" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2044,10 +2209,15 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
+      <c r="M34" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2104,10 +2274,15 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr">
+      <c r="M35" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2164,10 +2339,15 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L36" t="inlineStr">
+      <c r="M36" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2224,10 +2404,15 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr">
+      <c r="M37" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2284,10 +2469,15 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L38" t="inlineStr">
+      <c r="M38" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2344,10 +2534,15 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L39" t="inlineStr">
+      <c r="M39" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2404,10 +2599,15 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L40" t="inlineStr">
+      <c r="M40" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2464,10 +2664,15 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr">
+      <c r="M41" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2524,10 +2729,15 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr">
+      <c r="M42" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2584,10 +2794,15 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr">
+      <c r="M43" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2644,10 +2859,15 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L44" t="inlineStr">
+      <c r="M44" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2704,10 +2924,15 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr">
+      <c r="M45" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2764,10 +2989,15 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr">
+      <c r="M46" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2824,10 +3054,15 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L47" t="inlineStr">
+      <c r="M47" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2884,10 +3119,15 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L48" t="inlineStr">
+      <c r="M48" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2944,10 +3184,15 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L49" t="inlineStr">
+      <c r="M49" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3004,10 +3249,15 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L50" t="inlineStr">
+      <c r="M50" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3064,10 +3314,15 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr">
+      <c r="M51" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3124,10 +3379,15 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L52" t="inlineStr">
+      <c r="M52" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3184,10 +3444,15 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L53" t="inlineStr">
+      <c r="M53" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3244,10 +3509,15 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L54" t="inlineStr">
+      <c r="M54" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3304,10 +3574,15 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L55" t="inlineStr">
+      <c r="M55" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3364,10 +3639,15 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L56" t="inlineStr">
+      <c r="M56" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3424,10 +3704,15 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L57" t="inlineStr">
+      <c r="M57" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3484,10 +3769,15 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L58" t="inlineStr">
+      <c r="M58" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3544,10 +3834,15 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L59" t="inlineStr">
+      <c r="M59" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3604,10 +3899,15 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L60" t="inlineStr">
+      <c r="M60" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3664,10 +3964,15 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L61" t="inlineStr">
+      <c r="M61" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3724,10 +4029,15 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L62" t="inlineStr">
+      <c r="M62" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3784,10 +4094,15 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L63" t="inlineStr">
+      <c r="M63" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3844,10 +4159,15 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L64" t="inlineStr">
+      <c r="M64" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3904,10 +4224,15 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L65" t="inlineStr">
+      <c r="M65" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3964,10 +4289,15 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L66" t="inlineStr">
+      <c r="M66" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4024,10 +4354,15 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L67" t="inlineStr">
+      <c r="M67" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4084,10 +4419,15 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L68" t="inlineStr">
+      <c r="M68" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4144,10 +4484,15 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L69" t="inlineStr">
+      <c r="M69" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4204,10 +4549,15 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L70" t="inlineStr">
+      <c r="M70" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4264,10 +4614,15 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L71" t="inlineStr">
+      <c r="M71" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4324,10 +4679,15 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L72" t="inlineStr">
+      <c r="M72" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4384,10 +4744,15 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L73" t="inlineStr">
+      <c r="M73" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4444,10 +4809,15 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L74" t="inlineStr">
+      <c r="M74" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4504,10 +4874,15 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L75" t="inlineStr">
+      <c r="M75" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4564,10 +4939,15 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L76" t="inlineStr">
+      <c r="M76" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4624,10 +5004,15 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L77" t="inlineStr">
+      <c r="M77" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4684,10 +5069,15 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L78" t="inlineStr">
+      <c r="M78" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4744,10 +5134,15 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L79" t="inlineStr">
+      <c r="M79" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4804,10 +5199,15 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L80" t="inlineStr">
+      <c r="M80" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4864,10 +5264,15 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L81" t="inlineStr">
+      <c r="M81" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4924,10 +5329,15 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L82" t="inlineStr">
+      <c r="M82" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4984,10 +5394,15 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L83" t="inlineStr">
+      <c r="M83" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5044,10 +5459,15 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L84" t="inlineStr">
+      <c r="M84" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5104,10 +5524,15 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L85" t="inlineStr">
+      <c r="M85" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5164,10 +5589,15 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L86" t="inlineStr">
+      <c r="M86" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5224,10 +5654,15 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L87" t="inlineStr">
+      <c r="M87" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5284,10 +5719,15 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L88" t="inlineStr">
+      <c r="M88" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5344,10 +5784,15 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L89" t="inlineStr">
+      <c r="M89" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5399,15 +5844,20 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-06-24</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr">
+      <c r="L90" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L90" t="inlineStr">
+      <c r="M90" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5454,20 +5904,25 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t xml:space="preserve">200027494</t>
+          <t xml:space="preserve">200027486</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-02-01</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr">
+      <c r="L91" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L91" t="inlineStr">
+      <c r="M91" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5519,15 +5974,20 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-02-01</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr">
+      <c r="L92" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L92" t="inlineStr">
+      <c r="M92" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5574,20 +6034,25 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t xml:space="preserve">200027494</t>
+          <t xml:space="preserve">200027518</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-02-01</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr">
+      <c r="L93" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L93" t="inlineStr">
+      <c r="M93" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5639,15 +6104,20 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-02-01</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr">
+      <c r="L94" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L94" t="inlineStr">
+      <c r="M94" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5699,15 +6169,20 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-02-02</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr">
+      <c r="L95" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L95" t="inlineStr">
+      <c r="M95" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5759,15 +6234,20 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek Skive</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-03-12</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr">
+      <c r="L96" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L96" t="inlineStr">
+      <c r="M96" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5819,15 +6299,20 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek Skive</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-11-01</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr">
+      <c r="L97" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L97" t="inlineStr">
+      <c r="M97" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5879,15 +6364,20 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S (Skive)</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-01-12</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr">
+      <c r="L98" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L98" t="inlineStr">
+      <c r="M98" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5939,15 +6429,20 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S (Skive)</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-01-12</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr">
+      <c r="L99" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L99" t="inlineStr">
+      <c r="M99" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5999,15 +6494,20 @@
       </c>
       <c r="J100" t="inlineStr">
         <is>
+          <t xml:space="preserve">Grontmij | Carl Bro A/S</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-02-10</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr">
+      <c r="L100" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L100" t="inlineStr">
+      <c r="M100" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6059,15 +6559,20 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
+          <t xml:space="preserve">Grontmij | Carl Bro A/S</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-02-10</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr">
+      <c r="L101" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L101" t="inlineStr">
+      <c r="M101" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6119,15 +6624,20 @@
       </c>
       <c r="J102" t="inlineStr">
         <is>
+          <t xml:space="preserve">Grontmij | Carl Bro A/S</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-02-10</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr">
+      <c r="L102" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L102" t="inlineStr">
+      <c r="M102" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6179,15 +6689,20 @@
       </c>
       <c r="J103" t="inlineStr">
         <is>
+          <t xml:space="preserve">Grontmij | Carl Bro A/S</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-02-10</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr">
+      <c r="L103" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L103" t="inlineStr">
+      <c r="M103" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6239,15 +6754,20 @@
       </c>
       <c r="J104" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek Skive</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
           <t xml:space="preserve">2022-12-12</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr">
+      <c r="L104" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L104" t="inlineStr">
+      <c r="M104" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6299,15 +6819,20 @@
       </c>
       <c r="J105" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek Skive</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
           <t xml:space="preserve">2024-09-04</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr">
+      <c r="L105" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L105" t="inlineStr">
+      <c r="M105" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6359,15 +6884,20 @@
       </c>
       <c r="J106" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
           <t xml:space="preserve">2024-09-18</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr">
+      <c r="L106" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L106" t="inlineStr">
+      <c r="M106" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6419,15 +6949,20 @@
       </c>
       <c r="J107" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-01-29</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr">
+      <c r="L107" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L107" t="inlineStr">
+      <c r="M107" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6479,15 +7014,20 @@
       </c>
       <c r="J108" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiConsult</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-08-31</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr">
+      <c r="L108" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L108" t="inlineStr">
+      <c r="M108" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6539,15 +7079,20 @@
       </c>
       <c r="J109" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiConsult</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-09-06</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr">
+      <c r="L109" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L109" t="inlineStr">
+      <c r="M109" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6599,15 +7144,20 @@
       </c>
       <c r="J110" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiConsult</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-09-09</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr">
+      <c r="L110" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L110" t="inlineStr">
+      <c r="M110" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6659,15 +7209,20 @@
       </c>
       <c r="J111" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiConsult</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-09-09</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr">
+      <c r="L111" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L111" t="inlineStr">
+      <c r="M111" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6719,15 +7274,20 @@
       </c>
       <c r="J112" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiConsult</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-09-09</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr">
+      <c r="L112" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L112" t="inlineStr">
+      <c r="M112" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6779,15 +7339,20 @@
       </c>
       <c r="J113" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiConsult</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-09-19</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr">
+      <c r="L113" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L113" t="inlineStr">
+      <c r="M113" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6839,15 +7404,20 @@
       </c>
       <c r="J114" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiConsult</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-09-19</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr">
+      <c r="L114" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L114" t="inlineStr">
+      <c r="M114" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6899,15 +7469,20 @@
       </c>
       <c r="J115" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiConsult ApS</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-10-05</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr">
+      <c r="L115" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L115" t="inlineStr">
+      <c r="M115" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6959,15 +7534,20 @@
       </c>
       <c r="J116" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiConsult ApS</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-10-18</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr">
+      <c r="L116" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L116" t="inlineStr">
+      <c r="M116" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7019,15 +7599,20 @@
       </c>
       <c r="J117" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiConsult ApS</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-11-23</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr">
+      <c r="L117" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L117" t="inlineStr">
+      <c r="M117" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7079,15 +7664,20 @@
       </c>
       <c r="J118" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiConsult ApS</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-11-30</t>
         </is>
       </c>
-      <c r="K118" t="inlineStr">
+      <c r="L118" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L118" t="inlineStr">
+      <c r="M118" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7139,15 +7729,20 @@
       </c>
       <c r="J119" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiConsult ApS</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-11-30</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr">
+      <c r="L119" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L119" t="inlineStr">
+      <c r="M119" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7199,15 +7794,20 @@
       </c>
       <c r="J120" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiConsult ApS</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-12-02</t>
         </is>
       </c>
-      <c r="K120" t="inlineStr">
+      <c r="L120" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L120" t="inlineStr">
+      <c r="M120" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7259,15 +7859,20 @@
       </c>
       <c r="J121" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiConsult ApS</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-12-08</t>
         </is>
       </c>
-      <c r="K121" t="inlineStr">
+      <c r="L121" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L121" t="inlineStr">
+      <c r="M121" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7319,15 +7924,20 @@
       </c>
       <c r="J122" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiConsult ApS</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-12-08</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr">
+      <c r="L122" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L122" t="inlineStr">
+      <c r="M122" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7379,15 +7989,20 @@
       </c>
       <c r="J123" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiConsult ApS</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-12-08</t>
         </is>
       </c>
-      <c r="K123" t="inlineStr">
+      <c r="L123" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L123" t="inlineStr">
+      <c r="M123" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7439,15 +8054,20 @@
       </c>
       <c r="J124" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiConsult ApS</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-12-08</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr">
+      <c r="L124" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L124" t="inlineStr">
+      <c r="M124" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7499,15 +8119,20 @@
       </c>
       <c r="J125" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiConsult ApS</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-01-17</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr">
+      <c r="L125" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L125" t="inlineStr">
+      <c r="M125" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7559,15 +8184,20 @@
       </c>
       <c r="J126" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiConsult ApS</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-01-26</t>
         </is>
       </c>
-      <c r="K126" t="inlineStr">
+      <c r="L126" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L126" t="inlineStr">
+      <c r="M126" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7619,15 +8249,20 @@
       </c>
       <c r="J127" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiConsult ApS</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-01-26</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr">
+      <c r="L127" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L127" t="inlineStr">
+      <c r="M127" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7679,15 +8314,20 @@
       </c>
       <c r="J128" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiConsult ApS</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-05-22</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr">
+      <c r="L128" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L128" t="inlineStr">
+      <c r="M128" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7739,15 +8379,20 @@
       </c>
       <c r="J129" t="inlineStr">
         <is>
+          <t xml:space="preserve">Just A/S</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-07-10</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr">
+      <c r="L129" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L129" t="inlineStr">
+      <c r="M129" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7799,15 +8444,20 @@
       </c>
       <c r="J130" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-07-12</t>
         </is>
       </c>
-      <c r="K130" t="inlineStr">
+      <c r="L130" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L130" t="inlineStr">
+      <c r="M130" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7859,15 +8509,20 @@
       </c>
       <c r="J131" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiConsult ApS</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-08-31</t>
         </is>
       </c>
-      <c r="K131" t="inlineStr">
+      <c r="L131" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L131" t="inlineStr">
+      <c r="M131" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7919,15 +8574,20 @@
       </c>
       <c r="J132" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiConsult ApS</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-08-31</t>
         </is>
       </c>
-      <c r="K132" t="inlineStr">
+      <c r="L132" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L132" t="inlineStr">
+      <c r="M132" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7979,15 +8639,20 @@
       </c>
       <c r="J133" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiConsult ApS</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-09-11</t>
         </is>
       </c>
-      <c r="K133" t="inlineStr">
+      <c r="L133" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L133" t="inlineStr">
+      <c r="M133" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8039,15 +8704,20 @@
       </c>
       <c r="J134" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiConsult ApS</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-09-21</t>
         </is>
       </c>
-      <c r="K134" t="inlineStr">
+      <c r="L134" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L134" t="inlineStr">
+      <c r="M134" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8099,15 +8769,20 @@
       </c>
       <c r="J135" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiConsult ApS</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-09-25</t>
         </is>
       </c>
-      <c r="K135" t="inlineStr">
+      <c r="L135" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L135" t="inlineStr">
+      <c r="M135" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8159,15 +8834,20 @@
       </c>
       <c r="J136" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiConsult ApS</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-09-25</t>
         </is>
       </c>
-      <c r="K136" t="inlineStr">
+      <c r="L136" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L136" t="inlineStr">
+      <c r="M136" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8219,15 +8899,20 @@
       </c>
       <c r="J137" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiConsult ApS</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-10-23</t>
         </is>
       </c>
-      <c r="K137" t="inlineStr">
+      <c r="L137" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L137" t="inlineStr">
+      <c r="M137" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8279,15 +8964,20 @@
       </c>
       <c r="J138" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiConsult ApS</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-11-10</t>
         </is>
       </c>
-      <c r="K138" t="inlineStr">
+      <c r="L138" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L138" t="inlineStr">
+      <c r="M138" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8339,15 +9029,20 @@
       </c>
       <c r="J139" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiConsult ApS</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-11-10</t>
         </is>
       </c>
-      <c r="K139" t="inlineStr">
+      <c r="L139" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L139" t="inlineStr">
+      <c r="M139" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8399,15 +9094,20 @@
       </c>
       <c r="J140" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiConsult ApS</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-11-13</t>
         </is>
       </c>
-      <c r="K140" t="inlineStr">
+      <c r="L140" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L140" t="inlineStr">
+      <c r="M140" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8459,15 +9159,20 @@
       </c>
       <c r="J141" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiConsult ApS</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-11-16</t>
         </is>
       </c>
-      <c r="K141" t="inlineStr">
+      <c r="L141" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L141" t="inlineStr">
+      <c r="M141" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8519,15 +9224,20 @@
       </c>
       <c r="J142" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiConsult ApS</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-11-23</t>
         </is>
       </c>
-      <c r="K142" t="inlineStr">
+      <c r="L142" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L142" t="inlineStr">
+      <c r="M142" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8579,15 +9289,20 @@
       </c>
       <c r="J143" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiConsult ApS</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-12</t>
         </is>
       </c>
-      <c r="K143" t="inlineStr">
+      <c r="L143" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L143" t="inlineStr">
+      <c r="M143" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8639,15 +9354,20 @@
       </c>
       <c r="J144" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiConsult ApS</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-12</t>
         </is>
       </c>
-      <c r="K144" t="inlineStr">
+      <c r="L144" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L144" t="inlineStr">
+      <c r="M144" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8699,15 +9419,20 @@
       </c>
       <c r="J145" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiConsult ApS</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-12</t>
         </is>
       </c>
-      <c r="K145" t="inlineStr">
+      <c r="L145" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L145" t="inlineStr">
+      <c r="M145" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8759,15 +9484,20 @@
       </c>
       <c r="J146" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiConsult ApS</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-12</t>
         </is>
       </c>
-      <c r="K146" t="inlineStr">
+      <c r="L146" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L146" t="inlineStr">
+      <c r="M146" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8819,15 +9549,20 @@
       </c>
       <c r="J147" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiConsult ApS</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-12</t>
         </is>
       </c>
-      <c r="K147" t="inlineStr">
+      <c r="L147" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L147" t="inlineStr">
+      <c r="M147" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8879,15 +9614,20 @@
       </c>
       <c r="J148" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiConsult ApS</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-12</t>
         </is>
       </c>
-      <c r="K148" t="inlineStr">
+      <c r="L148" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L148" t="inlineStr">
+      <c r="M148" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8939,15 +9679,20 @@
       </c>
       <c r="J149" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiConsult ApS</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-12</t>
         </is>
       </c>
-      <c r="K149" t="inlineStr">
+      <c r="L149" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L149" t="inlineStr">
+      <c r="M149" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8999,15 +9744,20 @@
       </c>
       <c r="J150" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiConsult ApS</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-12</t>
         </is>
       </c>
-      <c r="K150" t="inlineStr">
+      <c r="L150" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L150" t="inlineStr">
+      <c r="M150" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9059,15 +9809,20 @@
       </c>
       <c r="J151" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiConsult ApS</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-14</t>
         </is>
       </c>
-      <c r="K151" t="inlineStr">
+      <c r="L151" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L151" t="inlineStr">
+      <c r="M151" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9119,15 +9874,20 @@
       </c>
       <c r="J152" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiConsult ApS</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-18</t>
         </is>
       </c>
-      <c r="K152" t="inlineStr">
+      <c r="L152" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L152" t="inlineStr">
+      <c r="M152" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9179,15 +9939,20 @@
       </c>
       <c r="J153" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiConsult ApS</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-21</t>
         </is>
       </c>
-      <c r="K153" t="inlineStr">
+      <c r="L153" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L153" t="inlineStr">
+      <c r="M153" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9239,15 +10004,20 @@
       </c>
       <c r="J154" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiConsult ApS</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-11-12</t>
         </is>
       </c>
-      <c r="K154" t="inlineStr">
+      <c r="L154" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L154" t="inlineStr">
+      <c r="M154" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9299,15 +10069,20 @@
       </c>
       <c r="J155" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiConsult ApS</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-11-19</t>
         </is>
       </c>
-      <c r="K155" t="inlineStr">
+      <c r="L155" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L155" t="inlineStr">
+      <c r="M155" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9359,15 +10134,20 @@
       </c>
       <c r="J156" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiConsult ApS</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-11-19</t>
         </is>
       </c>
-      <c r="K156" t="inlineStr">
+      <c r="L156" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L156" t="inlineStr">
+      <c r="M156" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9419,15 +10199,20 @@
       </c>
       <c r="J157" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiConsult ApS</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-09-01</t>
         </is>
       </c>
-      <c r="K157" t="inlineStr">
+      <c r="L157" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L157" t="inlineStr">
+      <c r="M157" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9479,15 +10264,20 @@
       </c>
       <c r="J158" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiConsult ApS</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-09-02</t>
         </is>
       </c>
-      <c r="K158" t="inlineStr">
+      <c r="L158" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L158" t="inlineStr">
+      <c r="M158" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9539,15 +10329,20 @@
       </c>
       <c r="J159" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiConsult ApS</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-09-30</t>
         </is>
       </c>
-      <c r="K159" t="inlineStr">
+      <c r="L159" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L159" t="inlineStr">
+      <c r="M159" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9599,15 +10394,20 @@
       </c>
       <c r="J160" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiConsult ApS</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-09-30</t>
         </is>
       </c>
-      <c r="K160" t="inlineStr">
+      <c r="L160" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L160" t="inlineStr">
+      <c r="M160" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9659,15 +10459,20 @@
       </c>
       <c r="J161" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiConsult ApS</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-09-30</t>
         </is>
       </c>
-      <c r="K161" t="inlineStr">
+      <c r="L161" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L161" t="inlineStr">
+      <c r="M161" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9719,15 +10524,20 @@
       </c>
       <c r="J162" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiConsult ApS</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-10-21</t>
         </is>
       </c>
-      <c r="K162" t="inlineStr">
+      <c r="L162" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L162" t="inlineStr">
+      <c r="M162" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9779,15 +10589,20 @@
       </c>
       <c r="J163" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiConsult ApS</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-12-16</t>
         </is>
       </c>
-      <c r="K163" t="inlineStr">
+      <c r="L163" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L163" t="inlineStr">
+      <c r="M163" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9839,15 +10654,20 @@
       </c>
       <c r="J164" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiConsult ApS</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-12-16</t>
         </is>
       </c>
-      <c r="K164" t="inlineStr">
+      <c r="L164" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L164" t="inlineStr">
+      <c r="M164" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9899,15 +10719,20 @@
       </c>
       <c r="J165" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiConsult ApS</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-02-16</t>
         </is>
       </c>
-      <c r="K165" t="inlineStr">
+      <c r="L165" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L165" t="inlineStr">
+      <c r="M165" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9959,15 +10784,20 @@
       </c>
       <c r="J166" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiConsult ApS</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-02-22</t>
         </is>
       </c>
-      <c r="K166" t="inlineStr">
+      <c r="L166" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L166" t="inlineStr">
+      <c r="M166" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10019,15 +10849,20 @@
       </c>
       <c r="J167" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiConsult ApS</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-02-26</t>
         </is>
       </c>
-      <c r="K167" t="inlineStr">
+      <c r="L167" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L167" t="inlineStr">
+      <c r="M167" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10079,15 +10914,20 @@
       </c>
       <c r="J168" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiConsult ApS</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-03-15</t>
         </is>
       </c>
-      <c r="K168" t="inlineStr">
+      <c r="L168" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L168" t="inlineStr">
+      <c r="M168" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10139,15 +10979,20 @@
       </c>
       <c r="J169" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiConsult ApS</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-03-19</t>
         </is>
       </c>
-      <c r="K169" t="inlineStr">
+      <c r="L169" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L169" t="inlineStr">
+      <c r="M169" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10199,15 +11044,20 @@
       </c>
       <c r="J170" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiConsult ApS</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-03-23</t>
         </is>
       </c>
-      <c r="K170" t="inlineStr">
+      <c r="L170" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L170" t="inlineStr">
+      <c r="M170" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10259,15 +11109,20 @@
       </c>
       <c r="J171" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiConsult ApS</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-04-07</t>
         </is>
       </c>
-      <c r="K171" t="inlineStr">
+      <c r="L171" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L171" t="inlineStr">
+      <c r="M171" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10319,15 +11174,20 @@
       </c>
       <c r="J172" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiConsult ApS</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-04-07</t>
         </is>
       </c>
-      <c r="K172" t="inlineStr">
+      <c r="L172" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L172" t="inlineStr">
+      <c r="M172" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10379,15 +11239,20 @@
       </c>
       <c r="J173" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiConsult ApS</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-08-20</t>
         </is>
       </c>
-      <c r="K173" t="inlineStr">
+      <c r="L173" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L173" t="inlineStr">
+      <c r="M173" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10439,15 +11304,20 @@
       </c>
       <c r="J174" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiConsult ApS</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-08-20</t>
         </is>
       </c>
-      <c r="K174" t="inlineStr">
+      <c r="L174" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L174" t="inlineStr">
+      <c r="M174" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10499,15 +11369,20 @@
       </c>
       <c r="J175" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiConsult ApS</t>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-08-20</t>
         </is>
       </c>
-      <c r="K175" t="inlineStr">
+      <c r="L175" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L175" t="inlineStr">
+      <c r="M175" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10559,15 +11434,20 @@
       </c>
       <c r="J176" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiConsult ApS</t>
+        </is>
+      </c>
+      <c r="K176" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-08-20</t>
         </is>
       </c>
-      <c r="K176" t="inlineStr">
+      <c r="L176" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L176" t="inlineStr">
+      <c r="M176" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10619,15 +11499,20 @@
       </c>
       <c r="J177" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiConsult ApS</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-08-20</t>
         </is>
       </c>
-      <c r="K177" t="inlineStr">
+      <c r="L177" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L177" t="inlineStr">
+      <c r="M177" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10679,15 +11564,20 @@
       </c>
       <c r="J178" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiConsult ApS</t>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-11-24</t>
         </is>
       </c>
-      <c r="K178" t="inlineStr">
+      <c r="L178" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L178" t="inlineStr">
+      <c r="M178" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10739,15 +11629,20 @@
       </c>
       <c r="J179" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiConsult ApS</t>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-01-06</t>
         </is>
       </c>
-      <c r="K179" t="inlineStr">
+      <c r="L179" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L179" t="inlineStr">
+      <c r="M179" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10799,15 +11694,20 @@
       </c>
       <c r="J180" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiConsult ApS</t>
+        </is>
+      </c>
+      <c r="K180" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-01-18</t>
         </is>
       </c>
-      <c r="K180" t="inlineStr">
+      <c r="L180" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L180" t="inlineStr">
+      <c r="M180" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10859,15 +11759,20 @@
       </c>
       <c r="J181" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiConsult ApS</t>
+        </is>
+      </c>
+      <c r="K181" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-01-18</t>
         </is>
       </c>
-      <c r="K181" t="inlineStr">
+      <c r="L181" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L181" t="inlineStr">
+      <c r="M181" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10919,15 +11824,20 @@
       </c>
       <c r="J182" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiConsult ApS</t>
+        </is>
+      </c>
+      <c r="K182" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-01-31</t>
         </is>
       </c>
-      <c r="K182" t="inlineStr">
+      <c r="L182" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L182" t="inlineStr">
+      <c r="M182" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10979,15 +11889,20 @@
       </c>
       <c r="J183" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiConsult ApS</t>
+        </is>
+      </c>
+      <c r="K183" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-02-01</t>
         </is>
       </c>
-      <c r="K183" t="inlineStr">
+      <c r="L183" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L183" t="inlineStr">
+      <c r="M183" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11039,15 +11954,20 @@
       </c>
       <c r="J184" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-02-15</t>
         </is>
       </c>
-      <c r="K184" t="inlineStr">
+      <c r="L184" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L184" t="inlineStr">
+      <c r="M184" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11099,15 +12019,20 @@
       </c>
       <c r="J185" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K185" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-03-15</t>
         </is>
       </c>
-      <c r="K185" t="inlineStr">
+      <c r="L185" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L185" t="inlineStr">
+      <c r="M185" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11159,15 +12084,20 @@
       </c>
       <c r="J186" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K186" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-03-15</t>
         </is>
       </c>
-      <c r="K186" t="inlineStr">
+      <c r="L186" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L186" t="inlineStr">
+      <c r="M186" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11219,15 +12149,20 @@
       </c>
       <c r="J187" t="inlineStr">
         <is>
+          <t xml:space="preserve">Xpert boligråd aps</t>
+        </is>
+      </c>
+      <c r="K187" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-03-15</t>
         </is>
       </c>
-      <c r="K187" t="inlineStr">
+      <c r="L187" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L187" t="inlineStr">
+      <c r="M187" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11279,15 +12214,20 @@
       </c>
       <c r="J188" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K188" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-03-15</t>
         </is>
       </c>
-      <c r="K188" t="inlineStr">
+      <c r="L188" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L188" t="inlineStr">
+      <c r="M188" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11339,15 +12279,20 @@
       </c>
       <c r="J189" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K189" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-03-15</t>
         </is>
       </c>
-      <c r="K189" t="inlineStr">
+      <c r="L189" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L189" t="inlineStr">
+      <c r="M189" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11394,20 +12339,25 @@
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t xml:space="preserve">311585352</t>
+          <t xml:space="preserve">311585347</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K190" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-03-15</t>
         </is>
       </c>
-      <c r="K190" t="inlineStr">
+      <c r="L190" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L190" t="inlineStr">
+      <c r="M190" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11459,15 +12409,20 @@
       </c>
       <c r="J191" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K191" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-03-15</t>
         </is>
       </c>
-      <c r="K191" t="inlineStr">
+      <c r="L191" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L191" t="inlineStr">
+      <c r="M191" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11519,15 +12474,20 @@
       </c>
       <c r="J192" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K192" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-04-21</t>
         </is>
       </c>
-      <c r="K192" t="inlineStr">
+      <c r="L192" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L192" t="inlineStr">
+      <c r="M192" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11579,15 +12539,20 @@
       </c>
       <c r="J193" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiConsult ApS</t>
+        </is>
+      </c>
+      <c r="K193" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-09-13</t>
         </is>
       </c>
-      <c r="K193" t="inlineStr">
+      <c r="L193" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L193" t="inlineStr">
+      <c r="M193" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11639,15 +12604,20 @@
       </c>
       <c r="J194" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiConsult ApS</t>
+        </is>
+      </c>
+      <c r="K194" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-09-13</t>
         </is>
       </c>
-      <c r="K194" t="inlineStr">
+      <c r="L194" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L194" t="inlineStr">
+      <c r="M194" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11699,15 +12669,20 @@
       </c>
       <c r="J195" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiConsult ApS</t>
+        </is>
+      </c>
+      <c r="K195" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-10-11</t>
         </is>
       </c>
-      <c r="K195" t="inlineStr">
+      <c r="L195" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L195" t="inlineStr">
+      <c r="M195" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11759,15 +12734,20 @@
       </c>
       <c r="J196" t="inlineStr">
         <is>
+          <t xml:space="preserve">Norconsult A/S</t>
+        </is>
+      </c>
+      <c r="K196" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-10-13</t>
         </is>
       </c>
-      <c r="K196" t="inlineStr">
+      <c r="L196" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L196" t="inlineStr">
+      <c r="M196" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11819,15 +12799,20 @@
       </c>
       <c r="J197" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiConsult ApS</t>
+        </is>
+      </c>
+      <c r="K197" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-10-17</t>
         </is>
       </c>
-      <c r="K197" t="inlineStr">
+      <c r="L197" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L197" t="inlineStr">
+      <c r="M197" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11879,15 +12864,20 @@
       </c>
       <c r="J198" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiConsult ApS</t>
+        </is>
+      </c>
+      <c r="K198" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-10-19</t>
         </is>
       </c>
-      <c r="K198" t="inlineStr">
+      <c r="L198" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L198" t="inlineStr">
+      <c r="M198" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11939,15 +12929,20 @@
       </c>
       <c r="J199" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiConsult ApS</t>
+        </is>
+      </c>
+      <c r="K199" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-03-11</t>
         </is>
       </c>
-      <c r="K199" t="inlineStr">
+      <c r="L199" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L199" t="inlineStr">
+      <c r="M199" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11999,15 +12994,20 @@
       </c>
       <c r="J200" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiConsult ApS</t>
+        </is>
+      </c>
+      <c r="K200" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-05-27</t>
         </is>
       </c>
-      <c r="K200" t="inlineStr">
+      <c r="L200" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L200" t="inlineStr">
+      <c r="M200" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12059,15 +13059,20 @@
       </c>
       <c r="J201" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiConsult ApS</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-05-27</t>
         </is>
       </c>
-      <c r="K201" t="inlineStr">
+      <c r="L201" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L201" t="inlineStr">
+      <c r="M201" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12119,15 +13124,20 @@
       </c>
       <c r="J202" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiConsult ApS</t>
+        </is>
+      </c>
+      <c r="K202" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-05-28</t>
         </is>
       </c>
-      <c r="K202" t="inlineStr">
+      <c r="L202" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L202" t="inlineStr">
+      <c r="M202" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12179,15 +13189,20 @@
       </c>
       <c r="J203" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiConsult ApS</t>
+        </is>
+      </c>
+      <c r="K203" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-06-18</t>
         </is>
       </c>
-      <c r="K203" t="inlineStr">
+      <c r="L203" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L203" t="inlineStr">
+      <c r="M203" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12239,15 +13254,20 @@
       </c>
       <c r="J204" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiConsult ApS</t>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-06-18</t>
         </is>
       </c>
-      <c r="K204" t="inlineStr">
+      <c r="L204" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L204" t="inlineStr">
+      <c r="M204" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12299,15 +13319,20 @@
       </c>
       <c r="J205" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiConsult ApS</t>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-03-03</t>
         </is>
       </c>
-      <c r="K205" t="inlineStr">
+      <c r="L205" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L205" t="inlineStr">
+      <c r="M205" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12359,15 +13384,20 @@
       </c>
       <c r="J206" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiConsult ApS</t>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-03-18</t>
         </is>
       </c>
-      <c r="K206" t="inlineStr">
+      <c r="L206" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L206" t="inlineStr">
+      <c r="M206" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12419,15 +13449,20 @@
       </c>
       <c r="J207" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiConsult ApS</t>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-03-27</t>
         </is>
       </c>
-      <c r="K207" t="inlineStr">
+      <c r="L207" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L207" t="inlineStr">
+      <c r="M207" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12479,15 +13514,20 @@
       </c>
       <c r="J208" t="inlineStr">
         <is>
+          <t xml:space="preserve">Lemvig Arkitektkontor Aps</t>
+        </is>
+      </c>
+      <c r="K208" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-04-14</t>
         </is>
       </c>
-      <c r="K208" t="inlineStr">
+      <c r="L208" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L208" t="inlineStr">
+      <c r="M208" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12539,15 +13579,20 @@
       </c>
       <c r="J209" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiConsult ApS</t>
+        </is>
+      </c>
+      <c r="K209" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-05-08</t>
         </is>
       </c>
-      <c r="K209" t="inlineStr">
+      <c r="L209" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L209" t="inlineStr">
+      <c r="M209" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12599,15 +13644,20 @@
       </c>
       <c r="J210" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiConsult ApS</t>
+        </is>
+      </c>
+      <c r="K210" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-05-22</t>
         </is>
       </c>
-      <c r="K210" t="inlineStr">
+      <c r="L210" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L210" t="inlineStr">
+      <c r="M210" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12659,15 +13709,20 @@
       </c>
       <c r="J211" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiConsult ApS</t>
+        </is>
+      </c>
+      <c r="K211" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-01-21</t>
         </is>
       </c>
-      <c r="K211" t="inlineStr">
+      <c r="L211" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L211" t="inlineStr">
+      <c r="M211" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12719,15 +13774,20 @@
       </c>
       <c r="J212" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiConsult ApS</t>
+        </is>
+      </c>
+      <c r="K212" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-02-10</t>
         </is>
       </c>
-      <c r="K212" t="inlineStr">
+      <c r="L212" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L212" t="inlineStr">
+      <c r="M212" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12779,15 +13839,20 @@
       </c>
       <c r="J213" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiConsult ApS</t>
+        </is>
+      </c>
+      <c r="K213" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-02-10</t>
         </is>
       </c>
-      <c r="K213" t="inlineStr">
+      <c r="L213" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L213" t="inlineStr">
+      <c r="M213" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12839,15 +13904,20 @@
       </c>
       <c r="J214" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiConsult ApS</t>
+        </is>
+      </c>
+      <c r="K214" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-02-11</t>
         </is>
       </c>
-      <c r="K214" t="inlineStr">
+      <c r="L214" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L214" t="inlineStr">
+      <c r="M214" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12899,15 +13969,20 @@
       </c>
       <c r="J215" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiConsult ApS</t>
+        </is>
+      </c>
+      <c r="K215" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-02-24</t>
         </is>
       </c>
-      <c r="K215" t="inlineStr">
+      <c r="L215" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L215" t="inlineStr">
+      <c r="M215" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12959,15 +14034,20 @@
       </c>
       <c r="J216" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiConsult ApS</t>
+        </is>
+      </c>
+      <c r="K216" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-03-24</t>
         </is>
       </c>
-      <c r="K216" t="inlineStr">
+      <c r="L216" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L216" t="inlineStr">
+      <c r="M216" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13019,15 +14099,20 @@
       </c>
       <c r="J217" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiConsult ApS</t>
+        </is>
+      </c>
+      <c r="K217" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-03-24</t>
         </is>
       </c>
-      <c r="K217" t="inlineStr">
+      <c r="L217" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L217" t="inlineStr">
+      <c r="M217" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13079,15 +14164,20 @@
       </c>
       <c r="J218" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiConsult ApS</t>
+        </is>
+      </c>
+      <c r="K218" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-05-18</t>
         </is>
       </c>
-      <c r="K218" t="inlineStr">
+      <c r="L218" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L218" t="inlineStr">
+      <c r="M218" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13139,21 +14229,26 @@
       </c>
       <c r="J219" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiConsult ApS</t>
+        </is>
+      </c>
+      <c r="K219" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-06-25</t>
         </is>
       </c>
-      <c r="K219" t="inlineStr">
+      <c r="L219" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L219" t="inlineStr">
+      <c r="M219" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L219"/>
+  <autoFilter ref="A1:M219"/>
 </worksheet>
 </file>
--- a/public/exports/29189579.xlsx
+++ b/public/exports/29189579.xlsx
@@ -6034,7 +6034,7 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t xml:space="preserve">200027518</t>
+          <t xml:space="preserve">200027494</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -7089,12 +7089,12 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -9999,7 +9999,7 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t xml:space="preserve">311346319</t>
+          <t xml:space="preserve">311346280</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
@@ -12144,12 +12144,12 @@
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t xml:space="preserve">311585357</t>
+          <t xml:space="preserve">311585347</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t xml:space="preserve">Xpert boligråd aps</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K187" t="inlineStr">
